--- a/projections/te_2026_combined.xlsx
+++ b/projections/te_2026_combined.xlsx
@@ -543,28 +543,28 @@
         <v>246.39</v>
       </c>
       <c r="H2" t="n">
-        <v>201.11</v>
+        <v>177.14</v>
       </c>
       <c r="I2" t="n">
-        <v>291.68</v>
+        <v>315.66</v>
       </c>
       <c r="J2" t="n">
         <v>197.79</v>
       </c>
       <c r="K2" t="n">
-        <v>159.43</v>
+        <v>139.12</v>
       </c>
       <c r="L2" t="n">
-        <v>236.16</v>
+        <v>256.47</v>
       </c>
       <c r="M2" t="n">
         <v>149.18</v>
       </c>
       <c r="N2" t="n">
-        <v>117.74</v>
+        <v>101.09</v>
       </c>
       <c r="O2" t="n">
-        <v>180.63</v>
+        <v>197.28</v>
       </c>
       <c r="P2" t="n">
         <v>252.3</v>
@@ -606,28 +606,28 @@
         <v>218.93</v>
       </c>
       <c r="H3" t="n">
-        <v>175.9</v>
+        <v>153.12</v>
       </c>
       <c r="I3" t="n">
-        <v>261.97</v>
+        <v>284.76</v>
       </c>
       <c r="J3" t="n">
         <v>175.23</v>
       </c>
       <c r="K3" t="n">
-        <v>138.76</v>
+        <v>119.46</v>
       </c>
       <c r="L3" t="n">
-        <v>211.72</v>
+        <v>231.04</v>
       </c>
       <c r="M3" t="n">
         <v>131.54</v>
       </c>
       <c r="N3" t="n">
-        <v>101.63</v>
+        <v>85.8</v>
       </c>
       <c r="O3" t="n">
-        <v>161.47</v>
+        <v>177.31</v>
       </c>
       <c r="P3" t="n">
         <v>256.3</v>
@@ -669,28 +669,28 @@
         <v>216.29</v>
       </c>
       <c r="H4" t="n">
-        <v>171.26</v>
+        <v>147.43</v>
       </c>
       <c r="I4" t="n">
-        <v>261.34</v>
+        <v>285.19</v>
       </c>
       <c r="J4" t="n">
         <v>172.34</v>
       </c>
       <c r="K4" t="n">
-        <v>133.89</v>
+        <v>113.54</v>
       </c>
       <c r="L4" t="n">
-        <v>210.81</v>
+        <v>231.18</v>
       </c>
       <c r="M4" t="n">
         <v>128.39</v>
       </c>
       <c r="N4" t="n">
-        <v>96.53</v>
+        <v>79.66</v>
       </c>
       <c r="O4" t="n">
-        <v>160.29</v>
+        <v>177.17</v>
       </c>
       <c r="P4" t="n">
         <v>240.1</v>
@@ -732,28 +732,28 @@
         <v>206.14</v>
       </c>
       <c r="H5" t="n">
-        <v>162.58</v>
+        <v>139.52</v>
       </c>
       <c r="I5" t="n">
-        <v>249.72</v>
+        <v>272.79</v>
       </c>
       <c r="J5" t="n">
         <v>165.76</v>
       </c>
       <c r="K5" t="n">
-        <v>128.5</v>
+        <v>108.78</v>
       </c>
       <c r="L5" t="n">
-        <v>203.03</v>
+        <v>222.76</v>
       </c>
       <c r="M5" t="n">
         <v>125.38</v>
       </c>
       <c r="N5" t="n">
-        <v>94.43000000000001</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>156.34</v>
+        <v>172.73</v>
       </c>
       <c r="P5" t="n">
         <v>187.3</v>
@@ -795,28 +795,28 @@
         <v>195.96</v>
       </c>
       <c r="H6" t="n">
-        <v>154.79</v>
+        <v>133</v>
       </c>
       <c r="I6" t="n">
-        <v>237.12</v>
+        <v>258.91</v>
       </c>
       <c r="J6" t="n">
         <v>155.42</v>
       </c>
       <c r="K6" t="n">
-        <v>120.57</v>
+        <v>102.12</v>
       </c>
       <c r="L6" t="n">
-        <v>190.26</v>
+        <v>208.7</v>
       </c>
       <c r="M6" t="n">
         <v>114.88</v>
       </c>
       <c r="N6" t="n">
-        <v>86.34999999999999</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>143.4</v>
+        <v>158.49</v>
       </c>
       <c r="P6" t="n">
         <v>195.2</v>
@@ -858,28 +858,28 @@
         <v>192.64</v>
       </c>
       <c r="H7" t="n">
-        <v>150.73</v>
+        <v>128.55</v>
       </c>
       <c r="I7" t="n">
-        <v>234.56</v>
+        <v>256.75</v>
       </c>
       <c r="J7" t="n">
         <v>154.81</v>
       </c>
       <c r="K7" t="n">
-        <v>119.01</v>
+        <v>100.06</v>
       </c>
       <c r="L7" t="n">
-        <v>190.62</v>
+        <v>209.58</v>
       </c>
       <c r="M7" t="n">
         <v>116.98</v>
       </c>
       <c r="N7" t="n">
-        <v>87.28</v>
+        <v>71.56</v>
       </c>
       <c r="O7" t="n">
-        <v>146.69</v>
+        <v>162.41</v>
       </c>
       <c r="P7" t="n">
         <v>184.8</v>
@@ -921,28 +921,28 @@
         <v>190.76</v>
       </c>
       <c r="H8" t="n">
-        <v>149.85</v>
+        <v>128.19</v>
       </c>
       <c r="I8" t="n">
-        <v>231.67</v>
+        <v>253.32</v>
       </c>
       <c r="J8" t="n">
         <v>148.06</v>
       </c>
       <c r="K8" t="n">
-        <v>113.63</v>
+        <v>95.41</v>
       </c>
       <c r="L8" t="n">
-        <v>182.48</v>
+        <v>200.7</v>
       </c>
       <c r="M8" t="n">
         <v>105.36</v>
       </c>
       <c r="N8" t="n">
-        <v>77.42</v>
+        <v>62.63</v>
       </c>
       <c r="O8" t="n">
-        <v>133.29</v>
+        <v>148.08</v>
       </c>
       <c r="P8" t="n">
         <v>221.2</v>
@@ -984,28 +984,28 @@
         <v>187.41</v>
       </c>
       <c r="H9" t="n">
-        <v>144.9</v>
+        <v>122.39</v>
       </c>
       <c r="I9" t="n">
-        <v>229.92</v>
+        <v>252.43</v>
       </c>
       <c r="J9" t="n">
         <v>153.76</v>
       </c>
       <c r="K9" t="n">
-        <v>117.01</v>
+        <v>97.55</v>
       </c>
       <c r="L9" t="n">
-        <v>190.52</v>
+        <v>209.98</v>
       </c>
       <c r="M9" t="n">
         <v>120.11</v>
       </c>
       <c r="N9" t="n">
-        <v>89.11</v>
+        <v>72.7</v>
       </c>
       <c r="O9" t="n">
-        <v>151.11</v>
+        <v>167.52</v>
       </c>
       <c r="P9" t="n">
         <v>197.5</v>
@@ -1047,28 +1047,28 @@
         <v>183.38</v>
       </c>
       <c r="H10" t="n">
-        <v>141.06</v>
+        <v>118.65</v>
       </c>
       <c r="I10" t="n">
-        <v>225.72</v>
+        <v>248.14</v>
       </c>
       <c r="J10" t="n">
         <v>151.08</v>
       </c>
       <c r="K10" t="n">
-        <v>114.4</v>
+        <v>94.98</v>
       </c>
       <c r="L10" t="n">
-        <v>187.79</v>
+        <v>207.22</v>
       </c>
       <c r="M10" t="n">
         <v>118.78</v>
       </c>
       <c r="N10" t="n">
-        <v>87.73</v>
+        <v>71.3</v>
       </c>
       <c r="O10" t="n">
-        <v>149.85</v>
+        <v>166.29</v>
       </c>
       <c r="P10" t="n">
         <v>175.3</v>
@@ -1110,28 +1110,28 @@
         <v>179.59</v>
       </c>
       <c r="H11" t="n">
-        <v>137.71</v>
+        <v>115.54</v>
       </c>
       <c r="I11" t="n">
-        <v>221.48</v>
+        <v>243.66</v>
       </c>
       <c r="J11" t="n">
         <v>149.62</v>
       </c>
       <c r="K11" t="n">
-        <v>113.17</v>
+        <v>93.88</v>
       </c>
       <c r="L11" t="n">
-        <v>186.08</v>
+        <v>205.38</v>
       </c>
       <c r="M11" t="n">
         <v>119.65</v>
       </c>
       <c r="N11" t="n">
-        <v>88.64</v>
+        <v>72.22</v>
       </c>
       <c r="O11" t="n">
-        <v>150.68</v>
+        <v>167.1</v>
       </c>
       <c r="P11" t="n">
         <v>210.6</v>
@@ -1173,28 +1173,28 @@
         <v>174.56</v>
       </c>
       <c r="H12" t="n">
-        <v>133.89</v>
+        <v>112.36</v>
       </c>
       <c r="I12" t="n">
-        <v>215.22</v>
+        <v>236.75</v>
       </c>
       <c r="J12" t="n">
         <v>139.16</v>
       </c>
       <c r="K12" t="n">
-        <v>104.39</v>
+        <v>85.98</v>
       </c>
       <c r="L12" t="n">
-        <v>173.92</v>
+        <v>192.32</v>
       </c>
       <c r="M12" t="n">
         <v>103.76</v>
       </c>
       <c r="N12" t="n">
-        <v>74.89</v>
+        <v>59.61</v>
       </c>
       <c r="O12" t="n">
-        <v>132.61</v>
+        <v>147.88</v>
       </c>
       <c r="P12" t="n">
         <v>154.4</v>
@@ -1236,28 +1236,28 @@
         <v>167.57</v>
       </c>
       <c r="H13" t="n">
-        <v>126.93</v>
+        <v>105.42</v>
       </c>
       <c r="I13" t="n">
-        <v>208.21</v>
+        <v>229.72</v>
       </c>
       <c r="J13" t="n">
         <v>132.11</v>
       </c>
       <c r="K13" t="n">
-        <v>97.38</v>
+        <v>79</v>
       </c>
       <c r="L13" t="n">
-        <v>166.84</v>
+        <v>185.22</v>
       </c>
       <c r="M13" t="n">
         <v>96.65000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>67.83</v>
+        <v>52.57</v>
       </c>
       <c r="O13" t="n">
-        <v>125.47</v>
+        <v>140.72</v>
       </c>
       <c r="P13" t="n">
         <v>148</v>
@@ -1299,28 +1299,28 @@
         <v>167.04</v>
       </c>
       <c r="H14" t="n">
-        <v>125.21</v>
+        <v>103.07</v>
       </c>
       <c r="I14" t="n">
-        <v>208.85</v>
+        <v>230.99</v>
       </c>
       <c r="J14" t="n">
         <v>136.23</v>
       </c>
       <c r="K14" t="n">
-        <v>99.91</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>172.53</v>
+        <v>191.74</v>
       </c>
       <c r="M14" t="n">
         <v>105.41</v>
       </c>
       <c r="N14" t="n">
-        <v>74.59999999999999</v>
+        <v>58.29</v>
       </c>
       <c r="O14" t="n">
-        <v>136.2</v>
+        <v>152.5</v>
       </c>
       <c r="P14" t="n">
         <v>161.6</v>
@@ -1362,28 +1362,28 @@
         <v>166.1</v>
       </c>
       <c r="H15" t="n">
-        <v>124.6</v>
+        <v>102.63</v>
       </c>
       <c r="I15" t="n">
-        <v>207.62</v>
+        <v>229.6</v>
       </c>
       <c r="J15" t="n">
         <v>135.38</v>
       </c>
       <c r="K15" t="n">
-        <v>99.38</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>171.39</v>
+        <v>190.46</v>
       </c>
       <c r="M15" t="n">
         <v>104.66</v>
       </c>
       <c r="N15" t="n">
-        <v>74.16</v>
+        <v>58.01</v>
       </c>
       <c r="O15" t="n">
-        <v>135.18</v>
+        <v>151.33</v>
       </c>
       <c r="P15" t="n">
         <v>155.1</v>
@@ -1425,28 +1425,28 @@
         <v>150.89</v>
       </c>
       <c r="H16" t="n">
-        <v>112.31</v>
+        <v>91.89</v>
       </c>
       <c r="I16" t="n">
-        <v>189.47</v>
+        <v>209.9</v>
       </c>
       <c r="J16" t="n">
         <v>118.19</v>
       </c>
       <c r="K16" t="n">
-        <v>85.29000000000001</v>
+        <v>67.87</v>
       </c>
       <c r="L16" t="n">
-        <v>151.1</v>
+        <v>168.52</v>
       </c>
       <c r="M16" t="n">
         <v>85.48999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>58.26</v>
+        <v>43.85</v>
       </c>
       <c r="O16" t="n">
-        <v>112.72</v>
+        <v>127.14</v>
       </c>
       <c r="P16" t="n">
         <v>148.6</v>
@@ -1488,28 +1488,28 @@
         <v>149.52</v>
       </c>
       <c r="H17" t="n">
-        <v>109.93</v>
+        <v>88.97</v>
       </c>
       <c r="I17" t="n">
-        <v>189.1</v>
+        <v>210.06</v>
       </c>
       <c r="J17" t="n">
         <v>123.02</v>
       </c>
       <c r="K17" t="n">
-        <v>88.54000000000001</v>
+        <v>70.28</v>
       </c>
       <c r="L17" t="n">
-        <v>157.5</v>
+        <v>175.75</v>
       </c>
       <c r="M17" t="n">
         <v>96.53</v>
       </c>
       <c r="N17" t="n">
-        <v>67.15000000000001</v>
+        <v>51.6</v>
       </c>
       <c r="O17" t="n">
-        <v>125.9</v>
+        <v>141.44</v>
       </c>
       <c r="P17" t="n">
         <v>160.9</v>
@@ -1551,28 +1551,28 @@
         <v>148.85</v>
       </c>
       <c r="H18" t="n">
-        <v>109.71</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>187.97</v>
+        <v>208.68</v>
       </c>
       <c r="J18" t="n">
         <v>120.3</v>
       </c>
       <c r="K18" t="n">
-        <v>86.45999999999999</v>
+        <v>68.55</v>
       </c>
       <c r="L18" t="n">
-        <v>154.12</v>
+        <v>172.02</v>
       </c>
       <c r="M18" t="n">
         <v>91.73999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>63.21</v>
+        <v>48.11</v>
       </c>
       <c r="O18" t="n">
-        <v>120.26</v>
+        <v>135.36</v>
       </c>
       <c r="P18" t="n">
         <v>161.2</v>
@@ -1614,28 +1614,28 @@
         <v>144.52</v>
       </c>
       <c r="H19" t="n">
-        <v>106.16</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>182.88</v>
+        <v>203.19</v>
       </c>
       <c r="J19" t="n">
         <v>114.93</v>
       </c>
       <c r="K19" t="n">
-        <v>81.97</v>
+        <v>64.52</v>
       </c>
       <c r="L19" t="n">
-        <v>147.89</v>
+        <v>165.34</v>
       </c>
       <c r="M19" t="n">
         <v>85.33</v>
       </c>
       <c r="N19" t="n">
-        <v>57.77</v>
+        <v>43.18</v>
       </c>
       <c r="O19" t="n">
-        <v>112.9</v>
+        <v>127.49</v>
       </c>
       <c r="P19" t="n">
         <v>147.8</v>
@@ -1677,28 +1677,28 @@
         <v>143.39</v>
       </c>
       <c r="H20" t="n">
-        <v>104.81</v>
+        <v>84.39</v>
       </c>
       <c r="I20" t="n">
-        <v>181.97</v>
+        <v>202.4</v>
       </c>
       <c r="J20" t="n">
         <v>116.52</v>
       </c>
       <c r="K20" t="n">
-        <v>83.09</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>149.97</v>
+        <v>167.67</v>
       </c>
       <c r="M20" t="n">
         <v>89.66</v>
       </c>
       <c r="N20" t="n">
-        <v>61.37</v>
+        <v>46.4</v>
       </c>
       <c r="O20" t="n">
-        <v>117.96</v>
+        <v>132.94</v>
       </c>
       <c r="P20" t="n">
         <v>133.3</v>
@@ -1740,28 +1740,28 @@
         <v>142.47</v>
       </c>
       <c r="H21" t="n">
-        <v>103.61</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>181.34</v>
+        <v>201.92</v>
       </c>
       <c r="J21" t="n">
         <v>116.14</v>
       </c>
       <c r="K21" t="n">
-        <v>82.37</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>149.92</v>
+        <v>167.8</v>
       </c>
       <c r="M21" t="n">
         <v>89.8</v>
       </c>
       <c r="N21" t="n">
-        <v>61.12</v>
+        <v>45.94</v>
       </c>
       <c r="O21" t="n">
-        <v>118.49</v>
+        <v>133.67</v>
       </c>
       <c r="P21" t="n">
         <v>156.8</v>
@@ -1803,28 +1803,28 @@
         <v>139.76</v>
       </c>
       <c r="H22" t="n">
-        <v>101.19</v>
+        <v>80.77</v>
       </c>
       <c r="I22" t="n">
-        <v>178.34</v>
+        <v>198.76</v>
       </c>
       <c r="J22" t="n">
         <v>112.73</v>
       </c>
       <c r="K22" t="n">
-        <v>79.31999999999999</v>
+        <v>61.64</v>
       </c>
       <c r="L22" t="n">
-        <v>146.15</v>
+        <v>163.84</v>
       </c>
       <c r="M22" t="n">
         <v>85.7</v>
       </c>
       <c r="N22" t="n">
-        <v>57.45</v>
+        <v>42.5</v>
       </c>
       <c r="O22" t="n">
-        <v>113.96</v>
+        <v>128.92</v>
       </c>
       <c r="P22" t="n">
         <v>125.3</v>
@@ -1866,28 +1866,28 @@
         <v>138.42</v>
       </c>
       <c r="H23" t="n">
-        <v>100.06</v>
+        <v>79.75</v>
       </c>
       <c r="I23" t="n">
-        <v>176.78</v>
+        <v>197.09</v>
       </c>
       <c r="J23" t="n">
         <v>107.95</v>
       </c>
       <c r="K23" t="n">
-        <v>75.06999999999999</v>
+        <v>57.66</v>
       </c>
       <c r="L23" t="n">
-        <v>140.83</v>
+        <v>158.24</v>
       </c>
       <c r="M23" t="n">
         <v>77.48999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>50.08</v>
+        <v>35.57</v>
       </c>
       <c r="O23" t="n">
-        <v>104.89</v>
+        <v>119.4</v>
       </c>
       <c r="P23" t="n">
         <v>166.6</v>
@@ -1929,28 +1929,28 @@
         <v>137.77</v>
       </c>
       <c r="H24" t="n">
-        <v>101.68</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>174.57</v>
+        <v>194.05</v>
       </c>
       <c r="J24" t="n">
         <v>109.73</v>
       </c>
       <c r="K24" t="n">
-        <v>78.89</v>
+        <v>62.57</v>
       </c>
       <c r="L24" t="n">
-        <v>141.28</v>
+        <v>157.98</v>
       </c>
       <c r="M24" t="n">
         <v>81.69</v>
       </c>
       <c r="N24" t="n">
-        <v>56.11</v>
+        <v>42.57</v>
       </c>
       <c r="O24" t="n">
-        <v>107.98</v>
+        <v>121.9</v>
       </c>
       <c r="P24" t="n">
         <v>139.3</v>
@@ -1992,28 +1992,28 @@
         <v>136.37</v>
       </c>
       <c r="H25" t="n">
-        <v>98.62</v>
+        <v>78.64</v>
       </c>
       <c r="I25" t="n">
-        <v>174.13</v>
+        <v>194.12</v>
       </c>
       <c r="J25" t="n">
         <v>108.26</v>
       </c>
       <c r="K25" t="n">
-        <v>75.78</v>
+        <v>58.58</v>
       </c>
       <c r="L25" t="n">
-        <v>140.76</v>
+        <v>157.96</v>
       </c>
       <c r="M25" t="n">
         <v>80.15000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>52.92</v>
+        <v>38.51</v>
       </c>
       <c r="O25" t="n">
-        <v>107.38</v>
+        <v>121.8</v>
       </c>
       <c r="P25" t="n">
         <v>132.6</v>
@@ -2055,28 +2055,28 @@
         <v>129.91</v>
       </c>
       <c r="H26" t="n">
-        <v>94.48</v>
+        <v>75.73</v>
       </c>
       <c r="I26" t="n">
-        <v>166.43</v>
+        <v>185.76</v>
       </c>
       <c r="J26" t="n">
         <v>101.15</v>
       </c>
       <c r="K26" t="n">
-        <v>71.04000000000001</v>
+        <v>55.1</v>
       </c>
       <c r="L26" t="n">
-        <v>132.35</v>
+        <v>148.86</v>
       </c>
       <c r="M26" t="n">
         <v>72.38</v>
       </c>
       <c r="N26" t="n">
-        <v>47.6</v>
+        <v>34.48</v>
       </c>
       <c r="O26" t="n">
-        <v>98.25</v>
+        <v>111.95</v>
       </c>
       <c r="P26" t="n">
         <v>152.8</v>
@@ -2118,28 +2118,28 @@
         <v>127.46</v>
       </c>
       <c r="H27" t="n">
-        <v>90.27</v>
+        <v>70.58</v>
       </c>
       <c r="I27" t="n">
-        <v>164.74</v>
+        <v>184.47</v>
       </c>
       <c r="J27" t="n">
         <v>100.44</v>
       </c>
       <c r="K27" t="n">
-        <v>68.41</v>
+        <v>51.46</v>
       </c>
       <c r="L27" t="n">
-        <v>132.56</v>
+        <v>149.56</v>
       </c>
       <c r="M27" t="n">
         <v>73.43000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>46.56</v>
+        <v>32.33</v>
       </c>
       <c r="O27" t="n">
-        <v>100.39</v>
+        <v>114.66</v>
       </c>
       <c r="P27" t="n">
         <v>104.7</v>
@@ -2181,28 +2181,28 @@
         <v>126.23</v>
       </c>
       <c r="H28" t="n">
-        <v>89.75</v>
+        <v>70.44</v>
       </c>
       <c r="I28" t="n">
-        <v>162.85</v>
+        <v>182.24</v>
       </c>
       <c r="J28" t="n">
         <v>102.39</v>
       </c>
       <c r="K28" t="n">
-        <v>70.76000000000001</v>
+        <v>54.01</v>
       </c>
       <c r="L28" t="n">
-        <v>134.17</v>
+        <v>150.99</v>
       </c>
       <c r="M28" t="n">
         <v>78.55</v>
       </c>
       <c r="N28" t="n">
-        <v>51.76</v>
+        <v>37.58</v>
       </c>
       <c r="O28" t="n">
-        <v>105.48</v>
+        <v>119.73</v>
       </c>
       <c r="P28" t="n">
         <v>125</v>
@@ -2244,28 +2244,28 @@
         <v>126.14</v>
       </c>
       <c r="H29" t="n">
-        <v>89.48999999999999</v>
+        <v>70.09</v>
       </c>
       <c r="I29" t="n">
-        <v>162.93</v>
+        <v>182.41</v>
       </c>
       <c r="J29" t="n">
         <v>101.24</v>
       </c>
       <c r="K29" t="n">
-        <v>69.54000000000001</v>
+        <v>52.76</v>
       </c>
       <c r="L29" t="n">
-        <v>133.08</v>
+        <v>149.94</v>
       </c>
       <c r="M29" t="n">
         <v>76.34</v>
       </c>
       <c r="N29" t="n">
-        <v>49.6</v>
+        <v>35.44</v>
       </c>
       <c r="O29" t="n">
-        <v>103.23</v>
+        <v>117.47</v>
       </c>
       <c r="P29" t="n">
         <v>105.8</v>
@@ -2307,28 +2307,28 @@
         <v>123.66</v>
       </c>
       <c r="H30" t="n">
-        <v>86.83</v>
+        <v>67.34</v>
       </c>
       <c r="I30" t="n">
-        <v>160.51</v>
+        <v>180.02</v>
       </c>
       <c r="J30" t="n">
         <v>100.03</v>
       </c>
       <c r="K30" t="n">
-        <v>68.03</v>
+        <v>51.09</v>
       </c>
       <c r="L30" t="n">
-        <v>132.06</v>
+        <v>149.01</v>
       </c>
       <c r="M30" t="n">
         <v>76.41</v>
       </c>
       <c r="N30" t="n">
-        <v>49.23</v>
+        <v>34.84</v>
       </c>
       <c r="O30" t="n">
-        <v>103.61</v>
+        <v>118.01</v>
       </c>
       <c r="P30" t="n">
         <v>109.1</v>
@@ -2370,28 +2370,28 @@
         <v>122.84</v>
       </c>
       <c r="H31" t="n">
-        <v>85.84999999999999</v>
+        <v>66.27</v>
       </c>
       <c r="I31" t="n">
-        <v>159.89</v>
+        <v>179.5</v>
       </c>
       <c r="J31" t="n">
         <v>97.23999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>65.27</v>
+        <v>48.34</v>
       </c>
       <c r="L31" t="n">
-        <v>129.26</v>
+        <v>146.21</v>
       </c>
       <c r="M31" t="n">
         <v>71.63</v>
       </c>
       <c r="N31" t="n">
-        <v>44.68</v>
+        <v>30.41</v>
       </c>
       <c r="O31" t="n">
-        <v>98.63</v>
+        <v>112.92</v>
       </c>
       <c r="P31" t="n">
         <v>106.4</v>
@@ -2433,28 +2433,28 @@
         <v>118.54</v>
       </c>
       <c r="H32" t="n">
-        <v>85.25</v>
+        <v>67.62</v>
       </c>
       <c r="I32" t="n">
-        <v>153.46</v>
+        <v>171.95</v>
       </c>
       <c r="J32" t="n">
         <v>94.23999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>65.84</v>
+        <v>50.8</v>
       </c>
       <c r="L32" t="n">
-        <v>124.27</v>
+        <v>140.17</v>
       </c>
       <c r="M32" t="n">
         <v>69.94</v>
       </c>
       <c r="N32" t="n">
-        <v>46.43</v>
+        <v>33.98</v>
       </c>
       <c r="O32" t="n">
-        <v>95.08</v>
+        <v>108.39</v>
       </c>
       <c r="P32" t="n">
         <v>128</v>
@@ -2496,28 +2496,28 @@
         <v>80.28</v>
       </c>
       <c r="H33" t="n">
-        <v>50.84</v>
+        <v>35.26</v>
       </c>
       <c r="I33" t="n">
-        <v>112.2</v>
+        <v>129.1</v>
       </c>
       <c r="J33" t="n">
         <v>64.11</v>
       </c>
       <c r="K33" t="n">
-        <v>38.66</v>
+        <v>25.19</v>
       </c>
       <c r="L33" t="n">
-        <v>92.04000000000001</v>
+        <v>106.82</v>
       </c>
       <c r="M33" t="n">
         <v>47.93</v>
       </c>
       <c r="N33" t="n">
-        <v>26.48</v>
+        <v>15.12</v>
       </c>
       <c r="O33" t="n">
-        <v>71.87</v>
+        <v>84.55</v>
       </c>
       <c r="P33" t="n">
         <v>48</v>
@@ -2559,28 +2559,28 @@
         <v>114.62</v>
       </c>
       <c r="H34" t="n">
-        <v>87.14</v>
+        <v>72.59</v>
       </c>
       <c r="I34" t="n">
-        <v>142.12</v>
+        <v>156.68</v>
       </c>
       <c r="J34" t="n">
         <v>90.23</v>
       </c>
       <c r="K34" t="n">
-        <v>67.25</v>
+        <v>55.08</v>
       </c>
       <c r="L34" t="n">
-        <v>113.23</v>
+        <v>125.4</v>
       </c>
       <c r="M34" t="n">
         <v>65.84</v>
       </c>
       <c r="N34" t="n">
-        <v>47.36</v>
+        <v>37.57</v>
       </c>
       <c r="O34" t="n">
-        <v>84.34</v>
+        <v>94.13</v>
       </c>
       <c r="P34" t="n">
         <v>113.9</v>
@@ -2622,28 +2622,28 @@
         <v>92.36</v>
       </c>
       <c r="H35" t="n">
-        <v>67.75</v>
+        <v>54.72</v>
       </c>
       <c r="I35" t="n">
-        <v>117.74</v>
+        <v>131.17</v>
       </c>
       <c r="J35" t="n">
         <v>74.23999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>53.51</v>
+        <v>42.53</v>
       </c>
       <c r="L35" t="n">
-        <v>95.73999999999999</v>
+        <v>107.12</v>
       </c>
       <c r="M35" t="n">
         <v>56.12</v>
       </c>
       <c r="N35" t="n">
-        <v>39.26</v>
+        <v>30.34</v>
       </c>
       <c r="O35" t="n">
-        <v>73.73999999999999</v>
+        <v>83.06</v>
       </c>
       <c r="P35" t="n">
         <v>61</v>
@@ -2685,28 +2685,28 @@
         <v>81.31</v>
       </c>
       <c r="H36" t="n">
-        <v>60</v>
+        <v>48.72</v>
       </c>
       <c r="I36" t="n">
-        <v>104.63</v>
+        <v>116.97</v>
       </c>
       <c r="J36" t="n">
         <v>65.11</v>
       </c>
       <c r="K36" t="n">
-        <v>47.47</v>
+        <v>38.13</v>
       </c>
       <c r="L36" t="n">
-        <v>84.77</v>
+        <v>95.17</v>
       </c>
       <c r="M36" t="n">
         <v>48.92</v>
       </c>
       <c r="N36" t="n">
-        <v>34.94</v>
+        <v>27.54</v>
       </c>
       <c r="O36" t="n">
-        <v>64.90000000000001</v>
+        <v>73.36</v>
       </c>
       <c r="P36" t="n">
         <v>67.5</v>
@@ -2748,28 +2748,28 @@
         <v>80.65000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>58.49</v>
+        <v>46.76</v>
       </c>
       <c r="I37" t="n">
-        <v>104.39</v>
+        <v>116.95</v>
       </c>
       <c r="J37" t="n">
         <v>65.28</v>
       </c>
       <c r="K37" t="n">
-        <v>46.7</v>
+        <v>36.86</v>
       </c>
       <c r="L37" t="n">
-        <v>85.45</v>
+        <v>96.13</v>
       </c>
       <c r="M37" t="n">
         <v>49.92</v>
       </c>
       <c r="N37" t="n">
-        <v>34.91</v>
+        <v>26.96</v>
       </c>
       <c r="O37" t="n">
-        <v>66.52</v>
+        <v>75.3</v>
       </c>
       <c r="P37" t="n">
         <v>66.7</v>
@@ -2811,28 +2811,28 @@
         <v>80.03</v>
       </c>
       <c r="H38" t="n">
-        <v>57.11</v>
+        <v>44.97</v>
       </c>
       <c r="I38" t="n">
-        <v>104.35</v>
+        <v>117.23</v>
       </c>
       <c r="J38" t="n">
         <v>63.08</v>
       </c>
       <c r="K38" t="n">
-        <v>43.91</v>
+        <v>33.76</v>
       </c>
       <c r="L38" t="n">
-        <v>83.65000000000001</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>46.13</v>
       </c>
       <c r="N38" t="n">
-        <v>30.71</v>
+        <v>22.55</v>
       </c>
       <c r="O38" t="n">
-        <v>62.95</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="P38" t="n">
         <v>99.3</v>
@@ -2874,28 +2874,28 @@
         <v>73.04000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>50.17</v>
+        <v>38.07</v>
       </c>
       <c r="I39" t="n">
-        <v>97.06999999999999</v>
+        <v>109.79</v>
       </c>
       <c r="J39" t="n">
         <v>58.79</v>
       </c>
       <c r="K39" t="n">
-        <v>39.36</v>
+        <v>29.08</v>
       </c>
       <c r="L39" t="n">
-        <v>79.38</v>
+        <v>90.28</v>
       </c>
       <c r="M39" t="n">
         <v>44.55</v>
       </c>
       <c r="N39" t="n">
-        <v>28.56</v>
+        <v>20.1</v>
       </c>
       <c r="O39" t="n">
-        <v>61.7</v>
+        <v>70.78</v>
       </c>
       <c r="P39" t="n">
         <v>70</v>
@@ -2937,28 +2937,28 @@
         <v>72.73</v>
       </c>
       <c r="H40" t="n">
-        <v>49.29</v>
+        <v>36.88</v>
       </c>
       <c r="I40" t="n">
-        <v>97.2</v>
+        <v>110.16</v>
       </c>
       <c r="J40" t="n">
         <v>57.32</v>
       </c>
       <c r="K40" t="n">
-        <v>37.46</v>
+        <v>26.94</v>
       </c>
       <c r="L40" t="n">
-        <v>78.22</v>
+        <v>89.28</v>
       </c>
       <c r="M40" t="n">
         <v>41.91</v>
       </c>
       <c r="N40" t="n">
-        <v>25.62</v>
+        <v>17</v>
       </c>
       <c r="O40" t="n">
-        <v>59.23</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="P40" t="n">
         <v>60.5</v>
@@ -3000,28 +3000,28 @@
         <v>69.72</v>
       </c>
       <c r="H41" t="n">
-        <v>49.52</v>
+        <v>38.83</v>
       </c>
       <c r="I41" t="n">
-        <v>92.23</v>
+        <v>104.14</v>
       </c>
       <c r="J41" t="n">
         <v>54.57</v>
       </c>
       <c r="K41" t="n">
-        <v>37.92</v>
+        <v>29.1</v>
       </c>
       <c r="L41" t="n">
-        <v>73.53</v>
+        <v>83.56</v>
       </c>
       <c r="M41" t="n">
         <v>39.41</v>
       </c>
       <c r="N41" t="n">
-        <v>26.31</v>
+        <v>19.37</v>
       </c>
       <c r="O41" t="n">
-        <v>54.82</v>
+        <v>62.97</v>
       </c>
       <c r="P41" t="n">
         <v>84.59999999999999</v>
@@ -3063,28 +3063,28 @@
         <v>57.06</v>
       </c>
       <c r="H42" t="n">
-        <v>36.78</v>
+        <v>26.04</v>
       </c>
       <c r="I42" t="n">
-        <v>79.3</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>45.4</v>
       </c>
       <c r="K42" t="n">
-        <v>28.23</v>
+        <v>19.14</v>
       </c>
       <c r="L42" t="n">
-        <v>64.53</v>
+        <v>74.66</v>
       </c>
       <c r="M42" t="n">
         <v>33.75</v>
       </c>
       <c r="N42" t="n">
-        <v>19.69</v>
+        <v>12.24</v>
       </c>
       <c r="O42" t="n">
-        <v>49.76</v>
+        <v>58.24</v>
       </c>
       <c r="P42" t="n">
         <v>69.09999999999999</v>
@@ -3126,28 +3126,28 @@
         <v>51.23</v>
       </c>
       <c r="H43" t="n">
-        <v>32.79</v>
+        <v>23.03</v>
       </c>
       <c r="I43" t="n">
-        <v>72.19</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="J43" t="n">
         <v>40.47</v>
       </c>
       <c r="K43" t="n">
-        <v>25.02</v>
+        <v>16.84</v>
       </c>
       <c r="L43" t="n">
-        <v>58.44</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M43" t="n">
         <v>29.72</v>
       </c>
       <c r="N43" t="n">
-        <v>17.26</v>
+        <v>10.66</v>
       </c>
       <c r="O43" t="n">
-        <v>44.71</v>
+        <v>52.64</v>
       </c>
       <c r="P43" t="n">
         <v>38.3</v>
@@ -3189,28 +3189,28 @@
         <v>49.99</v>
       </c>
       <c r="H44" t="n">
-        <v>30.82</v>
+        <v>20.67</v>
       </c>
       <c r="I44" t="n">
-        <v>71.45999999999999</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="J44" t="n">
         <v>38.99</v>
       </c>
       <c r="K44" t="n">
-        <v>22.83</v>
+        <v>14.28</v>
       </c>
       <c r="L44" t="n">
-        <v>57.43</v>
+        <v>67.19</v>
       </c>
       <c r="M44" t="n">
         <v>27.98</v>
       </c>
       <c r="N44" t="n">
-        <v>14.85</v>
+        <v>7.9</v>
       </c>
       <c r="O44" t="n">
-        <v>43.4</v>
+        <v>51.56</v>
       </c>
       <c r="P44" t="n">
         <v>61</v>
@@ -3252,28 +3252,28 @@
         <v>48.26</v>
       </c>
       <c r="H45" t="n">
-        <v>30.19</v>
+        <v>20.63</v>
       </c>
       <c r="I45" t="n">
-        <v>68.8</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="J45" t="n">
         <v>39.01</v>
       </c>
       <c r="K45" t="n">
-        <v>23.72</v>
+        <v>15.62</v>
       </c>
       <c r="L45" t="n">
-        <v>56.79</v>
+        <v>66.2</v>
       </c>
       <c r="M45" t="n">
         <v>29.77</v>
       </c>
       <c r="N45" t="n">
-        <v>17.25</v>
+        <v>10.62</v>
       </c>
       <c r="O45" t="n">
-        <v>44.78</v>
+        <v>52.72</v>
       </c>
       <c r="P45" t="n">
         <v>71.3</v>
@@ -3315,28 +3315,28 @@
         <v>47.8</v>
       </c>
       <c r="H46" t="n">
-        <v>29.15</v>
+        <v>19.27</v>
       </c>
       <c r="I46" t="n">
-        <v>68.77</v>
+        <v>79.87</v>
       </c>
       <c r="J46" t="n">
         <v>38.63</v>
       </c>
       <c r="K46" t="n">
-        <v>22.73</v>
+        <v>14.32</v>
       </c>
       <c r="L46" t="n">
-        <v>56.84</v>
+        <v>66.48</v>
       </c>
       <c r="M46" t="n">
         <v>29.46</v>
       </c>
       <c r="N46" t="n">
-        <v>16.32</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>44.91</v>
+        <v>53.09</v>
       </c>
       <c r="P46" t="n">
         <v>59.5</v>
@@ -3378,28 +3378,28 @@
         <v>47.73</v>
       </c>
       <c r="H47" t="n">
-        <v>30.36</v>
+        <v>21.16</v>
       </c>
       <c r="I47" t="n">
-        <v>67.86</v>
+        <v>78.52</v>
       </c>
       <c r="J47" t="n">
         <v>37.84</v>
       </c>
       <c r="K47" t="n">
-        <v>23.33</v>
+        <v>15.65</v>
       </c>
       <c r="L47" t="n">
-        <v>55.1</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="M47" t="n">
         <v>27.95</v>
       </c>
       <c r="N47" t="n">
-        <v>16.3</v>
+        <v>10.14</v>
       </c>
       <c r="O47" t="n">
-        <v>42.34</v>
+        <v>49.96</v>
       </c>
       <c r="P47" t="n">
         <v>43.9</v>
@@ -3441,28 +3441,28 @@
         <v>46.02</v>
       </c>
       <c r="H48" t="n">
-        <v>28</v>
+        <v>18.46</v>
       </c>
       <c r="I48" t="n">
-        <v>66.56</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="J48" t="n">
         <v>36.68</v>
       </c>
       <c r="K48" t="n">
-        <v>21.44</v>
+        <v>13.38</v>
       </c>
       <c r="L48" t="n">
-        <v>54.43</v>
+        <v>63.82</v>
       </c>
       <c r="M48" t="n">
         <v>27.33</v>
       </c>
       <c r="N48" t="n">
-        <v>14.88</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="O48" t="n">
-        <v>42.29</v>
+        <v>50.21</v>
       </c>
       <c r="P48" t="n">
         <v>49.8</v>
@@ -3504,28 +3504,28 @@
         <v>42.97</v>
       </c>
       <c r="H49" t="n">
-        <v>25.11</v>
+        <v>15.66</v>
       </c>
       <c r="I49" t="n">
-        <v>63.34</v>
+        <v>74.13</v>
       </c>
       <c r="J49" t="n">
         <v>34.28</v>
       </c>
       <c r="K49" t="n">
-        <v>19.11</v>
+        <v>11.08</v>
       </c>
       <c r="L49" t="n">
-        <v>51.97</v>
+        <v>61.34</v>
       </c>
       <c r="M49" t="n">
         <v>25.59</v>
       </c>
       <c r="N49" t="n">
-        <v>13.11</v>
+        <v>6.5</v>
       </c>
       <c r="O49" t="n">
-        <v>40.6</v>
+        <v>48.54</v>
       </c>
       <c r="P49" t="n">
         <v>33.2</v>
@@ -3567,28 +3567,28 @@
         <v>42.89</v>
       </c>
       <c r="H50" t="n">
-        <v>25.67</v>
+        <v>16.55</v>
       </c>
       <c r="I50" t="n">
-        <v>62.82</v>
+        <v>73.37</v>
       </c>
       <c r="J50" t="n">
         <v>33.92</v>
       </c>
       <c r="K50" t="n">
-        <v>19.43</v>
+        <v>11.76</v>
       </c>
       <c r="L50" t="n">
-        <v>51.12</v>
+        <v>60.22</v>
       </c>
       <c r="M50" t="n">
         <v>24.95</v>
       </c>
       <c r="N50" t="n">
-        <v>13.19</v>
+        <v>6.96</v>
       </c>
       <c r="O50" t="n">
-        <v>39.42</v>
+        <v>47.08</v>
       </c>
       <c r="P50" t="n">
         <v>63.8</v>
@@ -3630,28 +3630,28 @@
         <v>42.09</v>
       </c>
       <c r="H51" t="n">
-        <v>25.55</v>
+        <v>16.8</v>
       </c>
       <c r="I51" t="n">
-        <v>61.42</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="J51" t="n">
         <v>34.59</v>
       </c>
       <c r="K51" t="n">
-        <v>20.54</v>
+        <v>13.11</v>
       </c>
       <c r="L51" t="n">
-        <v>51.41</v>
+        <v>60.32</v>
       </c>
       <c r="M51" t="n">
         <v>27.08</v>
       </c>
       <c r="N51" t="n">
-        <v>15.53</v>
+        <v>9.42</v>
       </c>
       <c r="O51" t="n">
-        <v>41.41</v>
+        <v>49</v>
       </c>
       <c r="P51" t="n">
         <v>30.2</v>
@@ -3693,28 +3693,28 @@
         <v>41.86</v>
       </c>
       <c r="H52" t="n">
-        <v>25.22</v>
+        <v>16.41</v>
       </c>
       <c r="I52" t="n">
-        <v>61.22</v>
+        <v>71.47</v>
       </c>
       <c r="J52" t="n">
         <v>34.51</v>
       </c>
       <c r="K52" t="n">
-        <v>20.34</v>
+        <v>12.84</v>
       </c>
       <c r="L52" t="n">
-        <v>51.4</v>
+        <v>60.34</v>
       </c>
       <c r="M52" t="n">
         <v>27.15</v>
       </c>
       <c r="N52" t="n">
-        <v>15.45</v>
+        <v>9.26</v>
       </c>
       <c r="O52" t="n">
-        <v>41.57</v>
+        <v>49.2</v>
       </c>
       <c r="P52" t="n">
         <v>74.3</v>
@@ -3756,28 +3756,28 @@
         <v>41.46</v>
       </c>
       <c r="H53" t="n">
-        <v>24.32</v>
+        <v>15.24</v>
       </c>
       <c r="I53" t="n">
-        <v>61.31</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="J53" t="n">
         <v>32.86</v>
       </c>
       <c r="K53" t="n">
-        <v>18.39</v>
+        <v>10.73</v>
       </c>
       <c r="L53" t="n">
-        <v>50.04</v>
+        <v>59.14</v>
       </c>
       <c r="M53" t="n">
         <v>24.27</v>
       </c>
       <c r="N53" t="n">
-        <v>12.47</v>
+        <v>6.22</v>
       </c>
       <c r="O53" t="n">
-        <v>38.78</v>
+        <v>46.46</v>
       </c>
       <c r="P53" t="n">
         <v>34.9</v>
@@ -3819,28 +3819,28 @@
         <v>40.97</v>
       </c>
       <c r="H54" t="n">
-        <v>23.64</v>
+        <v>14.47</v>
       </c>
       <c r="I54" t="n">
-        <v>60.96</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="J54" t="n">
         <v>32.49</v>
       </c>
       <c r="K54" t="n">
-        <v>17.82</v>
+        <v>10.05</v>
       </c>
       <c r="L54" t="n">
-        <v>49.82</v>
+        <v>59</v>
       </c>
       <c r="M54" t="n">
         <v>24.01</v>
       </c>
       <c r="N54" t="n">
-        <v>11.99</v>
+        <v>5.63</v>
       </c>
       <c r="O54" t="n">
-        <v>38.7</v>
+        <v>46.47</v>
       </c>
       <c r="P54" t="n">
         <v>36.6</v>
@@ -3882,28 +3882,28 @@
         <v>40.19</v>
       </c>
       <c r="H55" t="n">
-        <v>22.66</v>
+        <v>13.38</v>
       </c>
       <c r="I55" t="n">
-        <v>60.26</v>
+        <v>70.88</v>
       </c>
       <c r="J55" t="n">
         <v>32.45</v>
       </c>
       <c r="K55" t="n">
-        <v>17.46</v>
+        <v>9.52</v>
       </c>
       <c r="L55" t="n">
-        <v>49.98</v>
+        <v>59.26</v>
       </c>
       <c r="M55" t="n">
         <v>24.7</v>
       </c>
       <c r="N55" t="n">
-        <v>12.24</v>
+        <v>5.65</v>
       </c>
       <c r="O55" t="n">
-        <v>39.69</v>
+        <v>47.63</v>
       </c>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
@@ -3941,28 +3941,28 @@
         <v>39.16</v>
       </c>
       <c r="H56" t="n">
-        <v>22.18</v>
+        <v>13.19</v>
       </c>
       <c r="I56" t="n">
-        <v>58.83</v>
+        <v>69.25</v>
       </c>
       <c r="J56" t="n">
         <v>31.29</v>
       </c>
       <c r="K56" t="n">
-        <v>16.87</v>
+        <v>9.23</v>
       </c>
       <c r="L56" t="n">
-        <v>48.41</v>
+        <v>57.47</v>
       </c>
       <c r="M56" t="n">
         <v>23.42</v>
       </c>
       <c r="N56" t="n">
-        <v>11.55</v>
+        <v>5.27</v>
       </c>
       <c r="O56" t="n">
-        <v>37.98</v>
+        <v>45.69</v>
       </c>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
@@ -4000,28 +4000,28 @@
         <v>38.54</v>
       </c>
       <c r="H57" t="n">
-        <v>22</v>
+        <v>13.24</v>
       </c>
       <c r="I57" t="n">
-        <v>57.92</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="J57" t="n">
         <v>30.28</v>
       </c>
       <c r="K57" t="n">
-        <v>16.35</v>
+        <v>8.98</v>
       </c>
       <c r="L57" t="n">
-        <v>47.05</v>
+        <v>55.92</v>
       </c>
       <c r="M57" t="n">
         <v>22.02</v>
       </c>
       <c r="N57" t="n">
-        <v>10.71</v>
+        <v>4.73</v>
       </c>
       <c r="O57" t="n">
-        <v>36.16</v>
+        <v>43.65</v>
       </c>
       <c r="P57" t="n">
         <v>20.6</v>
@@ -4063,28 +4063,28 @@
         <v>37.29</v>
       </c>
       <c r="H58" t="n">
-        <v>20.34</v>
+        <v>11.36</v>
       </c>
       <c r="I58" t="n">
-        <v>56.95</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="J58" t="n">
         <v>29.49</v>
       </c>
       <c r="K58" t="n">
-        <v>15.09</v>
+        <v>7.46</v>
       </c>
       <c r="L58" t="n">
-        <v>46.6</v>
+        <v>55.66</v>
       </c>
       <c r="M58" t="n">
         <v>21.7</v>
       </c>
       <c r="N58" t="n">
-        <v>9.83</v>
+        <v>3.55</v>
       </c>
       <c r="O58" t="n">
-        <v>36.26</v>
+        <v>43.97</v>
       </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
@@ -4122,28 +4122,28 @@
         <v>36.95</v>
       </c>
       <c r="H59" t="n">
-        <v>21.09</v>
+        <v>12.7</v>
       </c>
       <c r="I59" t="n">
-        <v>55.77</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="J59" t="n">
         <v>29.08</v>
       </c>
       <c r="K59" t="n">
-        <v>15.78</v>
+        <v>8.74</v>
       </c>
       <c r="L59" t="n">
-        <v>45.35</v>
+        <v>53.96</v>
       </c>
       <c r="M59" t="n">
         <v>21.22</v>
       </c>
       <c r="N59" t="n">
-        <v>10.47</v>
+        <v>4.78</v>
       </c>
       <c r="O59" t="n">
-        <v>34.93</v>
+        <v>42.19</v>
       </c>
       <c r="P59" t="n">
         <v>22.3</v>
@@ -4185,28 +4185,28 @@
         <v>36.82</v>
       </c>
       <c r="H60" t="n">
-        <v>20.21</v>
+        <v>11.42</v>
       </c>
       <c r="I60" t="n">
-        <v>56.19</v>
+        <v>66.44</v>
       </c>
       <c r="J60" t="n">
         <v>29.38</v>
       </c>
       <c r="K60" t="n">
-        <v>15.26</v>
+        <v>7.78</v>
       </c>
       <c r="L60" t="n">
-        <v>46.26</v>
+        <v>55.2</v>
       </c>
       <c r="M60" t="n">
         <v>21.95</v>
       </c>
       <c r="N60" t="n">
-        <v>10.31</v>
+        <v>4.15</v>
       </c>
       <c r="O60" t="n">
-        <v>36.35</v>
+        <v>43.97</v>
       </c>
       <c r="P60" t="n">
         <v>17.3</v>
@@ -4248,28 +4248,28 @@
         <v>36.61</v>
       </c>
       <c r="H61" t="n">
-        <v>19.54</v>
+        <v>10.5</v>
       </c>
       <c r="I61" t="n">
-        <v>56.33</v>
+        <v>66.77</v>
       </c>
       <c r="J61" t="n">
         <v>29.01</v>
       </c>
       <c r="K61" t="n">
-        <v>14.45</v>
+        <v>6.74</v>
       </c>
       <c r="L61" t="n">
-        <v>46.22</v>
+        <v>55.33</v>
       </c>
       <c r="M61" t="n">
         <v>21.42</v>
       </c>
       <c r="N61" t="n">
-        <v>9.369999999999999</v>
+        <v>2.99</v>
       </c>
       <c r="O61" t="n">
-        <v>36.11</v>
+        <v>43.89</v>
       </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
@@ -4307,28 +4307,28 @@
         <v>36.04</v>
       </c>
       <c r="H62" t="n">
-        <v>19.73</v>
+        <v>11.09</v>
       </c>
       <c r="I62" t="n">
-        <v>55.21</v>
+        <v>65.36</v>
       </c>
       <c r="J62" t="n">
         <v>28.52</v>
       </c>
       <c r="K62" t="n">
-        <v>14.7</v>
+        <v>7.38</v>
       </c>
       <c r="L62" t="n">
-        <v>45.19</v>
+        <v>54.01</v>
       </c>
       <c r="M62" t="n">
         <v>20.99</v>
       </c>
       <c r="N62" t="n">
-        <v>9.67</v>
+        <v>3.68</v>
       </c>
       <c r="O62" t="n">
-        <v>35.16</v>
+        <v>42.66</v>
       </c>
       <c r="P62" t="n">
         <v>35.1</v>
@@ -4370,28 +4370,28 @@
         <v>35.15</v>
       </c>
       <c r="H63" t="n">
-        <v>18.69</v>
+        <v>9.98</v>
       </c>
       <c r="I63" t="n">
-        <v>54.43</v>
+        <v>64.64</v>
       </c>
       <c r="J63" t="n">
         <v>27.48</v>
       </c>
       <c r="K63" t="n">
-        <v>13.55</v>
+        <v>6.18</v>
       </c>
       <c r="L63" t="n">
-        <v>44.25</v>
+        <v>53.12</v>
       </c>
       <c r="M63" t="n">
         <v>19.82</v>
       </c>
       <c r="N63" t="n">
-        <v>8.41</v>
+        <v>2.37</v>
       </c>
       <c r="O63" t="n">
-        <v>34.05</v>
+        <v>41.59</v>
       </c>
       <c r="P63" t="n">
         <v>30.7</v>
@@ -4433,28 +4433,28 @@
         <v>33.81</v>
       </c>
       <c r="H64" t="n">
-        <v>17.62</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>52.81</v>
+        <v>62.87</v>
       </c>
       <c r="J64" t="n">
         <v>26.9</v>
       </c>
       <c r="K64" t="n">
-        <v>13.11</v>
+        <v>5.81</v>
       </c>
       <c r="L64" t="n">
-        <v>43.51</v>
+        <v>52.3</v>
       </c>
       <c r="M64" t="n">
         <v>19.99</v>
       </c>
       <c r="N64" t="n">
-        <v>8.59</v>
+        <v>2.56</v>
       </c>
       <c r="O64" t="n">
-        <v>34.2</v>
+        <v>41.72</v>
       </c>
       <c r="P64" t="n">
         <v>23</v>
@@ -4496,28 +4496,28 @@
         <v>21.16</v>
       </c>
       <c r="H65" t="n">
-        <v>8.91</v>
+        <v>2.43</v>
       </c>
       <c r="I65" t="n">
-        <v>36.58</v>
+        <v>44.74</v>
       </c>
       <c r="J65" t="n">
         <v>17.47</v>
       </c>
       <c r="K65" t="n">
-        <v>6.98</v>
+        <v>1.42</v>
       </c>
       <c r="L65" t="n">
-        <v>31.14</v>
+        <v>38.38</v>
       </c>
       <c r="M65" t="n">
         <v>13.79</v>
       </c>
       <c r="N65" t="n">
-        <v>5.04</v>
+        <v>0.41</v>
       </c>
       <c r="O65" t="n">
-        <v>25.7</v>
+        <v>32.01</v>
       </c>
       <c r="P65" t="n">
         <v>9.9</v>
@@ -4670,28 +4670,28 @@
         <v>246.39</v>
       </c>
       <c r="H2" t="n">
-        <v>201.11</v>
+        <v>177.14</v>
       </c>
       <c r="I2" t="n">
-        <v>291.68</v>
+        <v>315.66</v>
       </c>
       <c r="J2" t="n">
         <v>197.79</v>
       </c>
       <c r="K2" t="n">
-        <v>159.43</v>
+        <v>139.12</v>
       </c>
       <c r="L2" t="n">
-        <v>236.16</v>
+        <v>256.47</v>
       </c>
       <c r="M2" t="n">
         <v>149.18</v>
       </c>
       <c r="N2" t="n">
-        <v>117.74</v>
+        <v>101.09</v>
       </c>
       <c r="O2" t="n">
-        <v>180.63</v>
+        <v>197.28</v>
       </c>
       <c r="P2" t="n">
         <v>252.3</v>
@@ -4733,28 +4733,28 @@
         <v>218.93</v>
       </c>
       <c r="H3" t="n">
-        <v>175.9</v>
+        <v>153.12</v>
       </c>
       <c r="I3" t="n">
-        <v>261.97</v>
+        <v>284.76</v>
       </c>
       <c r="J3" t="n">
         <v>175.23</v>
       </c>
       <c r="K3" t="n">
-        <v>138.76</v>
+        <v>119.46</v>
       </c>
       <c r="L3" t="n">
-        <v>211.72</v>
+        <v>231.04</v>
       </c>
       <c r="M3" t="n">
         <v>131.54</v>
       </c>
       <c r="N3" t="n">
-        <v>101.63</v>
+        <v>85.8</v>
       </c>
       <c r="O3" t="n">
-        <v>161.47</v>
+        <v>177.31</v>
       </c>
       <c r="P3" t="n">
         <v>256.3</v>
@@ -4796,28 +4796,28 @@
         <v>216.29</v>
       </c>
       <c r="H4" t="n">
-        <v>171.26</v>
+        <v>147.43</v>
       </c>
       <c r="I4" t="n">
-        <v>261.34</v>
+        <v>285.19</v>
       </c>
       <c r="J4" t="n">
         <v>172.34</v>
       </c>
       <c r="K4" t="n">
-        <v>133.89</v>
+        <v>113.54</v>
       </c>
       <c r="L4" t="n">
-        <v>210.81</v>
+        <v>231.18</v>
       </c>
       <c r="M4" t="n">
         <v>128.39</v>
       </c>
       <c r="N4" t="n">
-        <v>96.53</v>
+        <v>79.66</v>
       </c>
       <c r="O4" t="n">
-        <v>160.29</v>
+        <v>177.17</v>
       </c>
       <c r="P4" t="n">
         <v>240.1</v>
@@ -4859,28 +4859,28 @@
         <v>206.14</v>
       </c>
       <c r="H5" t="n">
-        <v>162.58</v>
+        <v>139.52</v>
       </c>
       <c r="I5" t="n">
-        <v>249.72</v>
+        <v>272.79</v>
       </c>
       <c r="J5" t="n">
         <v>165.76</v>
       </c>
       <c r="K5" t="n">
-        <v>128.5</v>
+        <v>108.78</v>
       </c>
       <c r="L5" t="n">
-        <v>203.03</v>
+        <v>222.76</v>
       </c>
       <c r="M5" t="n">
         <v>125.38</v>
       </c>
       <c r="N5" t="n">
-        <v>94.43000000000001</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>156.34</v>
+        <v>172.73</v>
       </c>
       <c r="P5" t="n">
         <v>187.3</v>
@@ -4922,28 +4922,28 @@
         <v>195.96</v>
       </c>
       <c r="H6" t="n">
-        <v>154.79</v>
+        <v>133</v>
       </c>
       <c r="I6" t="n">
-        <v>237.12</v>
+        <v>258.91</v>
       </c>
       <c r="J6" t="n">
         <v>155.42</v>
       </c>
       <c r="K6" t="n">
-        <v>120.57</v>
+        <v>102.12</v>
       </c>
       <c r="L6" t="n">
-        <v>190.26</v>
+        <v>208.7</v>
       </c>
       <c r="M6" t="n">
         <v>114.88</v>
       </c>
       <c r="N6" t="n">
-        <v>86.34999999999999</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>143.4</v>
+        <v>158.49</v>
       </c>
       <c r="P6" t="n">
         <v>195.2</v>
@@ -4985,28 +4985,28 @@
         <v>192.64</v>
       </c>
       <c r="H7" t="n">
-        <v>150.73</v>
+        <v>128.55</v>
       </c>
       <c r="I7" t="n">
-        <v>234.56</v>
+        <v>256.75</v>
       </c>
       <c r="J7" t="n">
         <v>154.81</v>
       </c>
       <c r="K7" t="n">
-        <v>119.01</v>
+        <v>100.06</v>
       </c>
       <c r="L7" t="n">
-        <v>190.62</v>
+        <v>209.58</v>
       </c>
       <c r="M7" t="n">
         <v>116.98</v>
       </c>
       <c r="N7" t="n">
-        <v>87.28</v>
+        <v>71.56</v>
       </c>
       <c r="O7" t="n">
-        <v>146.69</v>
+        <v>162.41</v>
       </c>
       <c r="P7" t="n">
         <v>184.8</v>
@@ -5048,28 +5048,28 @@
         <v>190.76</v>
       </c>
       <c r="H8" t="n">
-        <v>149.85</v>
+        <v>128.19</v>
       </c>
       <c r="I8" t="n">
-        <v>231.67</v>
+        <v>253.32</v>
       </c>
       <c r="J8" t="n">
         <v>148.06</v>
       </c>
       <c r="K8" t="n">
-        <v>113.63</v>
+        <v>95.41</v>
       </c>
       <c r="L8" t="n">
-        <v>182.48</v>
+        <v>200.7</v>
       </c>
       <c r="M8" t="n">
         <v>105.36</v>
       </c>
       <c r="N8" t="n">
-        <v>77.42</v>
+        <v>62.63</v>
       </c>
       <c r="O8" t="n">
-        <v>133.29</v>
+        <v>148.08</v>
       </c>
       <c r="P8" t="n">
         <v>221.2</v>
@@ -5111,28 +5111,28 @@
         <v>187.41</v>
       </c>
       <c r="H9" t="n">
-        <v>144.9</v>
+        <v>122.39</v>
       </c>
       <c r="I9" t="n">
-        <v>229.92</v>
+        <v>252.43</v>
       </c>
       <c r="J9" t="n">
         <v>153.76</v>
       </c>
       <c r="K9" t="n">
-        <v>117.01</v>
+        <v>97.55</v>
       </c>
       <c r="L9" t="n">
-        <v>190.52</v>
+        <v>209.98</v>
       </c>
       <c r="M9" t="n">
         <v>120.11</v>
       </c>
       <c r="N9" t="n">
-        <v>89.11</v>
+        <v>72.7</v>
       </c>
       <c r="O9" t="n">
-        <v>151.11</v>
+        <v>167.52</v>
       </c>
       <c r="P9" t="n">
         <v>197.5</v>
@@ -5174,28 +5174,28 @@
         <v>183.38</v>
       </c>
       <c r="H10" t="n">
-        <v>141.06</v>
+        <v>118.65</v>
       </c>
       <c r="I10" t="n">
-        <v>225.72</v>
+        <v>248.14</v>
       </c>
       <c r="J10" t="n">
         <v>151.08</v>
       </c>
       <c r="K10" t="n">
-        <v>114.4</v>
+        <v>94.98</v>
       </c>
       <c r="L10" t="n">
-        <v>187.79</v>
+        <v>207.22</v>
       </c>
       <c r="M10" t="n">
         <v>118.78</v>
       </c>
       <c r="N10" t="n">
-        <v>87.73</v>
+        <v>71.3</v>
       </c>
       <c r="O10" t="n">
-        <v>149.85</v>
+        <v>166.29</v>
       </c>
       <c r="P10" t="n">
         <v>175.3</v>
@@ -5237,28 +5237,28 @@
         <v>179.59</v>
       </c>
       <c r="H11" t="n">
-        <v>137.71</v>
+        <v>115.54</v>
       </c>
       <c r="I11" t="n">
-        <v>221.48</v>
+        <v>243.66</v>
       </c>
       <c r="J11" t="n">
         <v>149.62</v>
       </c>
       <c r="K11" t="n">
-        <v>113.17</v>
+        <v>93.88</v>
       </c>
       <c r="L11" t="n">
-        <v>186.08</v>
+        <v>205.38</v>
       </c>
       <c r="M11" t="n">
         <v>119.65</v>
       </c>
       <c r="N11" t="n">
-        <v>88.64</v>
+        <v>72.22</v>
       </c>
       <c r="O11" t="n">
-        <v>150.68</v>
+        <v>167.1</v>
       </c>
       <c r="P11" t="n">
         <v>210.6</v>
@@ -5300,28 +5300,28 @@
         <v>174.56</v>
       </c>
       <c r="H12" t="n">
-        <v>133.89</v>
+        <v>112.36</v>
       </c>
       <c r="I12" t="n">
-        <v>215.22</v>
+        <v>236.75</v>
       </c>
       <c r="J12" t="n">
         <v>139.16</v>
       </c>
       <c r="K12" t="n">
-        <v>104.39</v>
+        <v>85.98</v>
       </c>
       <c r="L12" t="n">
-        <v>173.92</v>
+        <v>192.32</v>
       </c>
       <c r="M12" t="n">
         <v>103.76</v>
       </c>
       <c r="N12" t="n">
-        <v>74.89</v>
+        <v>59.61</v>
       </c>
       <c r="O12" t="n">
-        <v>132.61</v>
+        <v>147.88</v>
       </c>
       <c r="P12" t="n">
         <v>154.4</v>
@@ -5363,28 +5363,28 @@
         <v>167.57</v>
       </c>
       <c r="H13" t="n">
-        <v>126.93</v>
+        <v>105.42</v>
       </c>
       <c r="I13" t="n">
-        <v>208.21</v>
+        <v>229.72</v>
       </c>
       <c r="J13" t="n">
         <v>132.11</v>
       </c>
       <c r="K13" t="n">
-        <v>97.38</v>
+        <v>79</v>
       </c>
       <c r="L13" t="n">
-        <v>166.84</v>
+        <v>185.22</v>
       </c>
       <c r="M13" t="n">
         <v>96.65000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>67.83</v>
+        <v>52.57</v>
       </c>
       <c r="O13" t="n">
-        <v>125.47</v>
+        <v>140.72</v>
       </c>
       <c r="P13" t="n">
         <v>148</v>
@@ -5426,28 +5426,28 @@
         <v>167.04</v>
       </c>
       <c r="H14" t="n">
-        <v>125.21</v>
+        <v>103.07</v>
       </c>
       <c r="I14" t="n">
-        <v>208.85</v>
+        <v>230.99</v>
       </c>
       <c r="J14" t="n">
         <v>136.23</v>
       </c>
       <c r="K14" t="n">
-        <v>99.91</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>172.53</v>
+        <v>191.74</v>
       </c>
       <c r="M14" t="n">
         <v>105.41</v>
       </c>
       <c r="N14" t="n">
-        <v>74.59999999999999</v>
+        <v>58.29</v>
       </c>
       <c r="O14" t="n">
-        <v>136.2</v>
+        <v>152.5</v>
       </c>
       <c r="P14" t="n">
         <v>161.6</v>
@@ -5489,28 +5489,28 @@
         <v>166.1</v>
       </c>
       <c r="H15" t="n">
-        <v>124.6</v>
+        <v>102.63</v>
       </c>
       <c r="I15" t="n">
-        <v>207.62</v>
+        <v>229.6</v>
       </c>
       <c r="J15" t="n">
         <v>135.38</v>
       </c>
       <c r="K15" t="n">
-        <v>99.38</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>171.39</v>
+        <v>190.46</v>
       </c>
       <c r="M15" t="n">
         <v>104.66</v>
       </c>
       <c r="N15" t="n">
-        <v>74.16</v>
+        <v>58.01</v>
       </c>
       <c r="O15" t="n">
-        <v>135.18</v>
+        <v>151.33</v>
       </c>
       <c r="P15" t="n">
         <v>155.1</v>
@@ -5552,28 +5552,28 @@
         <v>150.89</v>
       </c>
       <c r="H16" t="n">
-        <v>112.31</v>
+        <v>91.89</v>
       </c>
       <c r="I16" t="n">
-        <v>189.47</v>
+        <v>209.9</v>
       </c>
       <c r="J16" t="n">
         <v>118.19</v>
       </c>
       <c r="K16" t="n">
-        <v>85.29000000000001</v>
+        <v>67.87</v>
       </c>
       <c r="L16" t="n">
-        <v>151.1</v>
+        <v>168.52</v>
       </c>
       <c r="M16" t="n">
         <v>85.48999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>58.26</v>
+        <v>43.85</v>
       </c>
       <c r="O16" t="n">
-        <v>112.72</v>
+        <v>127.14</v>
       </c>
       <c r="P16" t="n">
         <v>148.6</v>
@@ -5615,28 +5615,28 @@
         <v>149.52</v>
       </c>
       <c r="H17" t="n">
-        <v>109.93</v>
+        <v>88.97</v>
       </c>
       <c r="I17" t="n">
-        <v>189.1</v>
+        <v>210.06</v>
       </c>
       <c r="J17" t="n">
         <v>123.02</v>
       </c>
       <c r="K17" t="n">
-        <v>88.54000000000001</v>
+        <v>70.28</v>
       </c>
       <c r="L17" t="n">
-        <v>157.5</v>
+        <v>175.75</v>
       </c>
       <c r="M17" t="n">
         <v>96.53</v>
       </c>
       <c r="N17" t="n">
-        <v>67.15000000000001</v>
+        <v>51.6</v>
       </c>
       <c r="O17" t="n">
-        <v>125.9</v>
+        <v>141.44</v>
       </c>
       <c r="P17" t="n">
         <v>160.9</v>
@@ -5678,28 +5678,28 @@
         <v>148.85</v>
       </c>
       <c r="H18" t="n">
-        <v>109.71</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>187.97</v>
+        <v>208.68</v>
       </c>
       <c r="J18" t="n">
         <v>120.3</v>
       </c>
       <c r="K18" t="n">
-        <v>86.45999999999999</v>
+        <v>68.55</v>
       </c>
       <c r="L18" t="n">
-        <v>154.12</v>
+        <v>172.02</v>
       </c>
       <c r="M18" t="n">
         <v>91.73999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>63.21</v>
+        <v>48.11</v>
       </c>
       <c r="O18" t="n">
-        <v>120.26</v>
+        <v>135.36</v>
       </c>
       <c r="P18" t="n">
         <v>161.2</v>
@@ -5741,28 +5741,28 @@
         <v>144.52</v>
       </c>
       <c r="H19" t="n">
-        <v>106.16</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>182.88</v>
+        <v>203.19</v>
       </c>
       <c r="J19" t="n">
         <v>114.93</v>
       </c>
       <c r="K19" t="n">
-        <v>81.97</v>
+        <v>64.52</v>
       </c>
       <c r="L19" t="n">
-        <v>147.89</v>
+        <v>165.34</v>
       </c>
       <c r="M19" t="n">
         <v>85.33</v>
       </c>
       <c r="N19" t="n">
-        <v>57.77</v>
+        <v>43.18</v>
       </c>
       <c r="O19" t="n">
-        <v>112.9</v>
+        <v>127.49</v>
       </c>
       <c r="P19" t="n">
         <v>147.8</v>
@@ -5804,28 +5804,28 @@
         <v>143.39</v>
       </c>
       <c r="H20" t="n">
-        <v>104.81</v>
+        <v>84.39</v>
       </c>
       <c r="I20" t="n">
-        <v>181.97</v>
+        <v>202.4</v>
       </c>
       <c r="J20" t="n">
         <v>116.52</v>
       </c>
       <c r="K20" t="n">
-        <v>83.09</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>149.97</v>
+        <v>167.67</v>
       </c>
       <c r="M20" t="n">
         <v>89.66</v>
       </c>
       <c r="N20" t="n">
-        <v>61.37</v>
+        <v>46.4</v>
       </c>
       <c r="O20" t="n">
-        <v>117.96</v>
+        <v>132.94</v>
       </c>
       <c r="P20" t="n">
         <v>133.3</v>
@@ -5867,28 +5867,28 @@
         <v>142.47</v>
       </c>
       <c r="H21" t="n">
-        <v>103.61</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>181.34</v>
+        <v>201.92</v>
       </c>
       <c r="J21" t="n">
         <v>116.14</v>
       </c>
       <c r="K21" t="n">
-        <v>82.37</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>149.92</v>
+        <v>167.8</v>
       </c>
       <c r="M21" t="n">
         <v>89.8</v>
       </c>
       <c r="N21" t="n">
-        <v>61.12</v>
+        <v>45.94</v>
       </c>
       <c r="O21" t="n">
-        <v>118.49</v>
+        <v>133.67</v>
       </c>
       <c r="P21" t="n">
         <v>156.8</v>
@@ -5930,28 +5930,28 @@
         <v>139.76</v>
       </c>
       <c r="H22" t="n">
-        <v>101.19</v>
+        <v>80.77</v>
       </c>
       <c r="I22" t="n">
-        <v>178.34</v>
+        <v>198.76</v>
       </c>
       <c r="J22" t="n">
         <v>112.73</v>
       </c>
       <c r="K22" t="n">
-        <v>79.31999999999999</v>
+        <v>61.64</v>
       </c>
       <c r="L22" t="n">
-        <v>146.15</v>
+        <v>163.84</v>
       </c>
       <c r="M22" t="n">
         <v>85.7</v>
       </c>
       <c r="N22" t="n">
-        <v>57.45</v>
+        <v>42.5</v>
       </c>
       <c r="O22" t="n">
-        <v>113.96</v>
+        <v>128.92</v>
       </c>
       <c r="P22" t="n">
         <v>125.3</v>
@@ -5993,28 +5993,28 @@
         <v>138.42</v>
       </c>
       <c r="H23" t="n">
-        <v>100.06</v>
+        <v>79.75</v>
       </c>
       <c r="I23" t="n">
-        <v>176.78</v>
+        <v>197.09</v>
       </c>
       <c r="J23" t="n">
         <v>107.95</v>
       </c>
       <c r="K23" t="n">
-        <v>75.06999999999999</v>
+        <v>57.66</v>
       </c>
       <c r="L23" t="n">
-        <v>140.83</v>
+        <v>158.24</v>
       </c>
       <c r="M23" t="n">
         <v>77.48999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>50.08</v>
+        <v>35.57</v>
       </c>
       <c r="O23" t="n">
-        <v>104.89</v>
+        <v>119.4</v>
       </c>
       <c r="P23" t="n">
         <v>166.6</v>
@@ -6056,28 +6056,28 @@
         <v>137.77</v>
       </c>
       <c r="H24" t="n">
-        <v>101.68</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>174.57</v>
+        <v>194.05</v>
       </c>
       <c r="J24" t="n">
         <v>109.73</v>
       </c>
       <c r="K24" t="n">
-        <v>78.89</v>
+        <v>62.57</v>
       </c>
       <c r="L24" t="n">
-        <v>141.28</v>
+        <v>157.98</v>
       </c>
       <c r="M24" t="n">
         <v>81.69</v>
       </c>
       <c r="N24" t="n">
-        <v>56.11</v>
+        <v>42.57</v>
       </c>
       <c r="O24" t="n">
-        <v>107.98</v>
+        <v>121.9</v>
       </c>
       <c r="P24" t="n">
         <v>139.3</v>
@@ -6119,28 +6119,28 @@
         <v>136.37</v>
       </c>
       <c r="H25" t="n">
-        <v>98.62</v>
+        <v>78.64</v>
       </c>
       <c r="I25" t="n">
-        <v>174.13</v>
+        <v>194.12</v>
       </c>
       <c r="J25" t="n">
         <v>108.26</v>
       </c>
       <c r="K25" t="n">
-        <v>75.78</v>
+        <v>58.58</v>
       </c>
       <c r="L25" t="n">
-        <v>140.76</v>
+        <v>157.96</v>
       </c>
       <c r="M25" t="n">
         <v>80.15000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>52.92</v>
+        <v>38.51</v>
       </c>
       <c r="O25" t="n">
-        <v>107.38</v>
+        <v>121.8</v>
       </c>
       <c r="P25" t="n">
         <v>132.6</v>
@@ -6182,28 +6182,28 @@
         <v>129.91</v>
       </c>
       <c r="H26" t="n">
-        <v>94.48</v>
+        <v>75.73</v>
       </c>
       <c r="I26" t="n">
-        <v>166.43</v>
+        <v>185.76</v>
       </c>
       <c r="J26" t="n">
         <v>101.15</v>
       </c>
       <c r="K26" t="n">
-        <v>71.04000000000001</v>
+        <v>55.1</v>
       </c>
       <c r="L26" t="n">
-        <v>132.35</v>
+        <v>148.86</v>
       </c>
       <c r="M26" t="n">
         <v>72.38</v>
       </c>
       <c r="N26" t="n">
-        <v>47.6</v>
+        <v>34.48</v>
       </c>
       <c r="O26" t="n">
-        <v>98.25</v>
+        <v>111.95</v>
       </c>
       <c r="P26" t="n">
         <v>152.8</v>
@@ -6245,28 +6245,28 @@
         <v>127.46</v>
       </c>
       <c r="H27" t="n">
-        <v>90.27</v>
+        <v>70.58</v>
       </c>
       <c r="I27" t="n">
-        <v>164.74</v>
+        <v>184.47</v>
       </c>
       <c r="J27" t="n">
         <v>100.44</v>
       </c>
       <c r="K27" t="n">
-        <v>68.41</v>
+        <v>51.46</v>
       </c>
       <c r="L27" t="n">
-        <v>132.56</v>
+        <v>149.56</v>
       </c>
       <c r="M27" t="n">
         <v>73.43000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>46.56</v>
+        <v>32.33</v>
       </c>
       <c r="O27" t="n">
-        <v>100.39</v>
+        <v>114.66</v>
       </c>
       <c r="P27" t="n">
         <v>104.7</v>
@@ -6308,28 +6308,28 @@
         <v>126.23</v>
       </c>
       <c r="H28" t="n">
-        <v>89.75</v>
+        <v>70.44</v>
       </c>
       <c r="I28" t="n">
-        <v>162.85</v>
+        <v>182.24</v>
       </c>
       <c r="J28" t="n">
         <v>102.39</v>
       </c>
       <c r="K28" t="n">
-        <v>70.76000000000001</v>
+        <v>54.01</v>
       </c>
       <c r="L28" t="n">
-        <v>134.17</v>
+        <v>150.99</v>
       </c>
       <c r="M28" t="n">
         <v>78.55</v>
       </c>
       <c r="N28" t="n">
-        <v>51.76</v>
+        <v>37.58</v>
       </c>
       <c r="O28" t="n">
-        <v>105.48</v>
+        <v>119.73</v>
       </c>
       <c r="P28" t="n">
         <v>125</v>
@@ -6371,28 +6371,28 @@
         <v>126.14</v>
       </c>
       <c r="H29" t="n">
-        <v>89.48999999999999</v>
+        <v>70.09</v>
       </c>
       <c r="I29" t="n">
-        <v>162.93</v>
+        <v>182.41</v>
       </c>
       <c r="J29" t="n">
         <v>101.24</v>
       </c>
       <c r="K29" t="n">
-        <v>69.54000000000001</v>
+        <v>52.76</v>
       </c>
       <c r="L29" t="n">
-        <v>133.08</v>
+        <v>149.94</v>
       </c>
       <c r="M29" t="n">
         <v>76.34</v>
       </c>
       <c r="N29" t="n">
-        <v>49.6</v>
+        <v>35.44</v>
       </c>
       <c r="O29" t="n">
-        <v>103.23</v>
+        <v>117.47</v>
       </c>
       <c r="P29" t="n">
         <v>105.8</v>
@@ -6434,28 +6434,28 @@
         <v>123.66</v>
       </c>
       <c r="H30" t="n">
-        <v>86.83</v>
+        <v>67.34</v>
       </c>
       <c r="I30" t="n">
-        <v>160.51</v>
+        <v>180.02</v>
       </c>
       <c r="J30" t="n">
         <v>100.03</v>
       </c>
       <c r="K30" t="n">
-        <v>68.03</v>
+        <v>51.09</v>
       </c>
       <c r="L30" t="n">
-        <v>132.06</v>
+        <v>149.01</v>
       </c>
       <c r="M30" t="n">
         <v>76.41</v>
       </c>
       <c r="N30" t="n">
-        <v>49.23</v>
+        <v>34.84</v>
       </c>
       <c r="O30" t="n">
-        <v>103.61</v>
+        <v>118.01</v>
       </c>
       <c r="P30" t="n">
         <v>109.1</v>
@@ -6497,28 +6497,28 @@
         <v>122.84</v>
       </c>
       <c r="H31" t="n">
-        <v>85.84999999999999</v>
+        <v>66.27</v>
       </c>
       <c r="I31" t="n">
-        <v>159.89</v>
+        <v>179.5</v>
       </c>
       <c r="J31" t="n">
         <v>97.23999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>65.27</v>
+        <v>48.34</v>
       </c>
       <c r="L31" t="n">
-        <v>129.26</v>
+        <v>146.21</v>
       </c>
       <c r="M31" t="n">
         <v>71.63</v>
       </c>
       <c r="N31" t="n">
-        <v>44.68</v>
+        <v>30.41</v>
       </c>
       <c r="O31" t="n">
-        <v>98.63</v>
+        <v>112.92</v>
       </c>
       <c r="P31" t="n">
         <v>106.4</v>
@@ -6560,28 +6560,28 @@
         <v>118.54</v>
       </c>
       <c r="H32" t="n">
-        <v>85.25</v>
+        <v>67.62</v>
       </c>
       <c r="I32" t="n">
-        <v>153.46</v>
+        <v>171.95</v>
       </c>
       <c r="J32" t="n">
         <v>94.23999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>65.84</v>
+        <v>50.8</v>
       </c>
       <c r="L32" t="n">
-        <v>124.27</v>
+        <v>140.17</v>
       </c>
       <c r="M32" t="n">
         <v>69.94</v>
       </c>
       <c r="N32" t="n">
-        <v>46.43</v>
+        <v>33.98</v>
       </c>
       <c r="O32" t="n">
-        <v>95.08</v>
+        <v>108.39</v>
       </c>
       <c r="P32" t="n">
         <v>128</v>
@@ -6623,28 +6623,28 @@
         <v>80.28</v>
       </c>
       <c r="H33" t="n">
-        <v>50.84</v>
+        <v>35.26</v>
       </c>
       <c r="I33" t="n">
-        <v>112.2</v>
+        <v>129.1</v>
       </c>
       <c r="J33" t="n">
         <v>64.11</v>
       </c>
       <c r="K33" t="n">
-        <v>38.66</v>
+        <v>25.19</v>
       </c>
       <c r="L33" t="n">
-        <v>92.04000000000001</v>
+        <v>106.82</v>
       </c>
       <c r="M33" t="n">
         <v>47.93</v>
       </c>
       <c r="N33" t="n">
-        <v>26.48</v>
+        <v>15.12</v>
       </c>
       <c r="O33" t="n">
-        <v>71.87</v>
+        <v>84.55</v>
       </c>
       <c r="P33" t="n">
         <v>48</v>
@@ -6797,28 +6797,28 @@
         <v>114.62</v>
       </c>
       <c r="H2" t="n">
-        <v>87.14</v>
+        <v>72.59</v>
       </c>
       <c r="I2" t="n">
-        <v>142.12</v>
+        <v>156.68</v>
       </c>
       <c r="J2" t="n">
         <v>90.23</v>
       </c>
       <c r="K2" t="n">
-        <v>67.25</v>
+        <v>55.08</v>
       </c>
       <c r="L2" t="n">
-        <v>113.23</v>
+        <v>125.4</v>
       </c>
       <c r="M2" t="n">
         <v>65.84</v>
       </c>
       <c r="N2" t="n">
-        <v>47.36</v>
+        <v>37.57</v>
       </c>
       <c r="O2" t="n">
-        <v>84.34</v>
+        <v>94.13</v>
       </c>
       <c r="P2" t="n">
         <v>113.9</v>
@@ -6860,28 +6860,28 @@
         <v>92.36</v>
       </c>
       <c r="H3" t="n">
-        <v>67.75</v>
+        <v>54.72</v>
       </c>
       <c r="I3" t="n">
-        <v>117.74</v>
+        <v>131.17</v>
       </c>
       <c r="J3" t="n">
         <v>74.23999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>53.51</v>
+        <v>42.53</v>
       </c>
       <c r="L3" t="n">
-        <v>95.73999999999999</v>
+        <v>107.12</v>
       </c>
       <c r="M3" t="n">
         <v>56.12</v>
       </c>
       <c r="N3" t="n">
-        <v>39.26</v>
+        <v>30.34</v>
       </c>
       <c r="O3" t="n">
-        <v>73.73999999999999</v>
+        <v>83.06</v>
       </c>
       <c r="P3" t="n">
         <v>61</v>
@@ -6923,28 +6923,28 @@
         <v>81.31</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>48.72</v>
       </c>
       <c r="I4" t="n">
-        <v>104.63</v>
+        <v>116.97</v>
       </c>
       <c r="J4" t="n">
         <v>65.11</v>
       </c>
       <c r="K4" t="n">
-        <v>47.47</v>
+        <v>38.13</v>
       </c>
       <c r="L4" t="n">
-        <v>84.77</v>
+        <v>95.17</v>
       </c>
       <c r="M4" t="n">
         <v>48.92</v>
       </c>
       <c r="N4" t="n">
-        <v>34.94</v>
+        <v>27.54</v>
       </c>
       <c r="O4" t="n">
-        <v>64.90000000000001</v>
+        <v>73.36</v>
       </c>
       <c r="P4" t="n">
         <v>67.5</v>
@@ -6986,28 +6986,28 @@
         <v>80.65000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>58.49</v>
+        <v>46.76</v>
       </c>
       <c r="I5" t="n">
-        <v>104.39</v>
+        <v>116.95</v>
       </c>
       <c r="J5" t="n">
         <v>65.28</v>
       </c>
       <c r="K5" t="n">
-        <v>46.7</v>
+        <v>36.86</v>
       </c>
       <c r="L5" t="n">
-        <v>85.45</v>
+        <v>96.13</v>
       </c>
       <c r="M5" t="n">
         <v>49.92</v>
       </c>
       <c r="N5" t="n">
-        <v>34.91</v>
+        <v>26.96</v>
       </c>
       <c r="O5" t="n">
-        <v>66.52</v>
+        <v>75.3</v>
       </c>
       <c r="P5" t="n">
         <v>66.7</v>
@@ -7049,28 +7049,28 @@
         <v>80.03</v>
       </c>
       <c r="H6" t="n">
-        <v>57.11</v>
+        <v>44.97</v>
       </c>
       <c r="I6" t="n">
-        <v>104.35</v>
+        <v>117.23</v>
       </c>
       <c r="J6" t="n">
         <v>63.08</v>
       </c>
       <c r="K6" t="n">
-        <v>43.91</v>
+        <v>33.76</v>
       </c>
       <c r="L6" t="n">
-        <v>83.65000000000001</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>46.13</v>
       </c>
       <c r="N6" t="n">
-        <v>30.71</v>
+        <v>22.55</v>
       </c>
       <c r="O6" t="n">
-        <v>62.95</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="P6" t="n">
         <v>99.3</v>
@@ -7112,28 +7112,28 @@
         <v>73.04000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>50.17</v>
+        <v>38.07</v>
       </c>
       <c r="I7" t="n">
-        <v>97.06999999999999</v>
+        <v>109.79</v>
       </c>
       <c r="J7" t="n">
         <v>58.79</v>
       </c>
       <c r="K7" t="n">
-        <v>39.36</v>
+        <v>29.08</v>
       </c>
       <c r="L7" t="n">
-        <v>79.38</v>
+        <v>90.28</v>
       </c>
       <c r="M7" t="n">
         <v>44.55</v>
       </c>
       <c r="N7" t="n">
-        <v>28.56</v>
+        <v>20.1</v>
       </c>
       <c r="O7" t="n">
-        <v>61.7</v>
+        <v>70.78</v>
       </c>
       <c r="P7" t="n">
         <v>70</v>
@@ -7175,28 +7175,28 @@
         <v>72.73</v>
       </c>
       <c r="H8" t="n">
-        <v>49.29</v>
+        <v>36.88</v>
       </c>
       <c r="I8" t="n">
-        <v>97.2</v>
+        <v>110.16</v>
       </c>
       <c r="J8" t="n">
         <v>57.32</v>
       </c>
       <c r="K8" t="n">
-        <v>37.46</v>
+        <v>26.94</v>
       </c>
       <c r="L8" t="n">
-        <v>78.22</v>
+        <v>89.28</v>
       </c>
       <c r="M8" t="n">
         <v>41.91</v>
       </c>
       <c r="N8" t="n">
-        <v>25.62</v>
+        <v>17</v>
       </c>
       <c r="O8" t="n">
-        <v>59.23</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="P8" t="n">
         <v>60.5</v>
@@ -7238,28 +7238,28 @@
         <v>69.72</v>
       </c>
       <c r="H9" t="n">
-        <v>49.52</v>
+        <v>38.83</v>
       </c>
       <c r="I9" t="n">
-        <v>92.23</v>
+        <v>104.14</v>
       </c>
       <c r="J9" t="n">
         <v>54.57</v>
       </c>
       <c r="K9" t="n">
-        <v>37.92</v>
+        <v>29.1</v>
       </c>
       <c r="L9" t="n">
-        <v>73.53</v>
+        <v>83.56</v>
       </c>
       <c r="M9" t="n">
         <v>39.41</v>
       </c>
       <c r="N9" t="n">
-        <v>26.31</v>
+        <v>19.37</v>
       </c>
       <c r="O9" t="n">
-        <v>54.82</v>
+        <v>62.97</v>
       </c>
       <c r="P9" t="n">
         <v>84.59999999999999</v>
@@ -7301,28 +7301,28 @@
         <v>57.06</v>
       </c>
       <c r="H10" t="n">
-        <v>36.78</v>
+        <v>26.04</v>
       </c>
       <c r="I10" t="n">
-        <v>79.3</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="J10" t="n">
         <v>45.4</v>
       </c>
       <c r="K10" t="n">
-        <v>28.23</v>
+        <v>19.14</v>
       </c>
       <c r="L10" t="n">
-        <v>64.53</v>
+        <v>74.66</v>
       </c>
       <c r="M10" t="n">
         <v>33.75</v>
       </c>
       <c r="N10" t="n">
-        <v>19.69</v>
+        <v>12.24</v>
       </c>
       <c r="O10" t="n">
-        <v>49.76</v>
+        <v>58.24</v>
       </c>
       <c r="P10" t="n">
         <v>69.09999999999999</v>
@@ -7364,28 +7364,28 @@
         <v>51.23</v>
       </c>
       <c r="H11" t="n">
-        <v>32.79</v>
+        <v>23.03</v>
       </c>
       <c r="I11" t="n">
-        <v>72.19</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="J11" t="n">
         <v>40.47</v>
       </c>
       <c r="K11" t="n">
-        <v>25.02</v>
+        <v>16.84</v>
       </c>
       <c r="L11" t="n">
-        <v>58.44</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>29.72</v>
       </c>
       <c r="N11" t="n">
-        <v>17.26</v>
+        <v>10.66</v>
       </c>
       <c r="O11" t="n">
-        <v>44.71</v>
+        <v>52.64</v>
       </c>
       <c r="P11" t="n">
         <v>38.3</v>
@@ -7427,28 +7427,28 @@
         <v>49.99</v>
       </c>
       <c r="H12" t="n">
-        <v>30.82</v>
+        <v>20.67</v>
       </c>
       <c r="I12" t="n">
-        <v>71.45999999999999</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="J12" t="n">
         <v>38.99</v>
       </c>
       <c r="K12" t="n">
-        <v>22.83</v>
+        <v>14.28</v>
       </c>
       <c r="L12" t="n">
-        <v>57.43</v>
+        <v>67.19</v>
       </c>
       <c r="M12" t="n">
         <v>27.98</v>
       </c>
       <c r="N12" t="n">
-        <v>14.85</v>
+        <v>7.9</v>
       </c>
       <c r="O12" t="n">
-        <v>43.4</v>
+        <v>51.56</v>
       </c>
       <c r="P12" t="n">
         <v>61</v>
@@ -7490,28 +7490,28 @@
         <v>48.26</v>
       </c>
       <c r="H13" t="n">
-        <v>30.19</v>
+        <v>20.63</v>
       </c>
       <c r="I13" t="n">
-        <v>68.8</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>39.01</v>
       </c>
       <c r="K13" t="n">
-        <v>23.72</v>
+        <v>15.62</v>
       </c>
       <c r="L13" t="n">
-        <v>56.79</v>
+        <v>66.2</v>
       </c>
       <c r="M13" t="n">
         <v>29.77</v>
       </c>
       <c r="N13" t="n">
-        <v>17.25</v>
+        <v>10.62</v>
       </c>
       <c r="O13" t="n">
-        <v>44.78</v>
+        <v>52.72</v>
       </c>
       <c r="P13" t="n">
         <v>71.3</v>
@@ -7553,28 +7553,28 @@
         <v>47.8</v>
       </c>
       <c r="H14" t="n">
-        <v>29.15</v>
+        <v>19.27</v>
       </c>
       <c r="I14" t="n">
-        <v>68.77</v>
+        <v>79.87</v>
       </c>
       <c r="J14" t="n">
         <v>38.63</v>
       </c>
       <c r="K14" t="n">
-        <v>22.73</v>
+        <v>14.32</v>
       </c>
       <c r="L14" t="n">
-        <v>56.84</v>
+        <v>66.48</v>
       </c>
       <c r="M14" t="n">
         <v>29.46</v>
       </c>
       <c r="N14" t="n">
-        <v>16.32</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>44.91</v>
+        <v>53.09</v>
       </c>
       <c r="P14" t="n">
         <v>59.5</v>
@@ -7616,28 +7616,28 @@
         <v>47.73</v>
       </c>
       <c r="H15" t="n">
-        <v>30.36</v>
+        <v>21.16</v>
       </c>
       <c r="I15" t="n">
-        <v>67.86</v>
+        <v>78.52</v>
       </c>
       <c r="J15" t="n">
         <v>37.84</v>
       </c>
       <c r="K15" t="n">
-        <v>23.33</v>
+        <v>15.65</v>
       </c>
       <c r="L15" t="n">
-        <v>55.1</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="M15" t="n">
         <v>27.95</v>
       </c>
       <c r="N15" t="n">
-        <v>16.3</v>
+        <v>10.14</v>
       </c>
       <c r="O15" t="n">
-        <v>42.34</v>
+        <v>49.96</v>
       </c>
       <c r="P15" t="n">
         <v>43.9</v>
@@ -7679,28 +7679,28 @@
         <v>46.02</v>
       </c>
       <c r="H16" t="n">
-        <v>28</v>
+        <v>18.46</v>
       </c>
       <c r="I16" t="n">
-        <v>66.56</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="J16" t="n">
         <v>36.68</v>
       </c>
       <c r="K16" t="n">
-        <v>21.44</v>
+        <v>13.38</v>
       </c>
       <c r="L16" t="n">
-        <v>54.43</v>
+        <v>63.82</v>
       </c>
       <c r="M16" t="n">
         <v>27.33</v>
       </c>
       <c r="N16" t="n">
-        <v>14.88</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>42.29</v>
+        <v>50.21</v>
       </c>
       <c r="P16" t="n">
         <v>49.8</v>
@@ -7742,28 +7742,28 @@
         <v>42.97</v>
       </c>
       <c r="H17" t="n">
-        <v>25.11</v>
+        <v>15.66</v>
       </c>
       <c r="I17" t="n">
-        <v>63.34</v>
+        <v>74.13</v>
       </c>
       <c r="J17" t="n">
         <v>34.28</v>
       </c>
       <c r="K17" t="n">
-        <v>19.11</v>
+        <v>11.08</v>
       </c>
       <c r="L17" t="n">
-        <v>51.97</v>
+        <v>61.34</v>
       </c>
       <c r="M17" t="n">
         <v>25.59</v>
       </c>
       <c r="N17" t="n">
-        <v>13.11</v>
+        <v>6.5</v>
       </c>
       <c r="O17" t="n">
-        <v>40.6</v>
+        <v>48.54</v>
       </c>
       <c r="P17" t="n">
         <v>33.2</v>
@@ -7805,28 +7805,28 @@
         <v>42.89</v>
       </c>
       <c r="H18" t="n">
-        <v>25.67</v>
+        <v>16.55</v>
       </c>
       <c r="I18" t="n">
-        <v>62.82</v>
+        <v>73.37</v>
       </c>
       <c r="J18" t="n">
         <v>33.92</v>
       </c>
       <c r="K18" t="n">
-        <v>19.43</v>
+        <v>11.76</v>
       </c>
       <c r="L18" t="n">
-        <v>51.12</v>
+        <v>60.22</v>
       </c>
       <c r="M18" t="n">
         <v>24.95</v>
       </c>
       <c r="N18" t="n">
-        <v>13.19</v>
+        <v>6.96</v>
       </c>
       <c r="O18" t="n">
-        <v>39.42</v>
+        <v>47.08</v>
       </c>
       <c r="P18" t="n">
         <v>63.8</v>
@@ -7868,28 +7868,28 @@
         <v>42.09</v>
       </c>
       <c r="H19" t="n">
-        <v>25.55</v>
+        <v>16.8</v>
       </c>
       <c r="I19" t="n">
-        <v>61.42</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="J19" t="n">
         <v>34.59</v>
       </c>
       <c r="K19" t="n">
-        <v>20.54</v>
+        <v>13.11</v>
       </c>
       <c r="L19" t="n">
-        <v>51.41</v>
+        <v>60.32</v>
       </c>
       <c r="M19" t="n">
         <v>27.08</v>
       </c>
       <c r="N19" t="n">
-        <v>15.53</v>
+        <v>9.42</v>
       </c>
       <c r="O19" t="n">
-        <v>41.41</v>
+        <v>49</v>
       </c>
       <c r="P19" t="n">
         <v>30.2</v>
@@ -7931,28 +7931,28 @@
         <v>41.86</v>
       </c>
       <c r="H20" t="n">
-        <v>25.22</v>
+        <v>16.41</v>
       </c>
       <c r="I20" t="n">
-        <v>61.22</v>
+        <v>71.47</v>
       </c>
       <c r="J20" t="n">
         <v>34.51</v>
       </c>
       <c r="K20" t="n">
-        <v>20.34</v>
+        <v>12.84</v>
       </c>
       <c r="L20" t="n">
-        <v>51.4</v>
+        <v>60.34</v>
       </c>
       <c r="M20" t="n">
         <v>27.15</v>
       </c>
       <c r="N20" t="n">
-        <v>15.45</v>
+        <v>9.26</v>
       </c>
       <c r="O20" t="n">
-        <v>41.57</v>
+        <v>49.2</v>
       </c>
       <c r="P20" t="n">
         <v>74.3</v>
@@ -7994,28 +7994,28 @@
         <v>41.46</v>
       </c>
       <c r="H21" t="n">
-        <v>24.32</v>
+        <v>15.24</v>
       </c>
       <c r="I21" t="n">
-        <v>61.31</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="J21" t="n">
         <v>32.86</v>
       </c>
       <c r="K21" t="n">
-        <v>18.39</v>
+        <v>10.73</v>
       </c>
       <c r="L21" t="n">
-        <v>50.04</v>
+        <v>59.14</v>
       </c>
       <c r="M21" t="n">
         <v>24.27</v>
       </c>
       <c r="N21" t="n">
-        <v>12.47</v>
+        <v>6.22</v>
       </c>
       <c r="O21" t="n">
-        <v>38.78</v>
+        <v>46.46</v>
       </c>
       <c r="P21" t="n">
         <v>34.9</v>
@@ -8057,28 +8057,28 @@
         <v>40.97</v>
       </c>
       <c r="H22" t="n">
-        <v>23.64</v>
+        <v>14.47</v>
       </c>
       <c r="I22" t="n">
-        <v>60.96</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="J22" t="n">
         <v>32.49</v>
       </c>
       <c r="K22" t="n">
-        <v>17.82</v>
+        <v>10.05</v>
       </c>
       <c r="L22" t="n">
-        <v>49.82</v>
+        <v>59</v>
       </c>
       <c r="M22" t="n">
         <v>24.01</v>
       </c>
       <c r="N22" t="n">
-        <v>11.99</v>
+        <v>5.63</v>
       </c>
       <c r="O22" t="n">
-        <v>38.7</v>
+        <v>46.47</v>
       </c>
       <c r="P22" t="n">
         <v>36.6</v>
@@ -8120,28 +8120,28 @@
         <v>40.19</v>
       </c>
       <c r="H23" t="n">
-        <v>22.66</v>
+        <v>13.38</v>
       </c>
       <c r="I23" t="n">
-        <v>60.26</v>
+        <v>70.88</v>
       </c>
       <c r="J23" t="n">
         <v>32.45</v>
       </c>
       <c r="K23" t="n">
-        <v>17.46</v>
+        <v>9.52</v>
       </c>
       <c r="L23" t="n">
-        <v>49.98</v>
+        <v>59.26</v>
       </c>
       <c r="M23" t="n">
         <v>24.7</v>
       </c>
       <c r="N23" t="n">
-        <v>12.24</v>
+        <v>5.65</v>
       </c>
       <c r="O23" t="n">
-        <v>39.69</v>
+        <v>47.63</v>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
@@ -8179,28 +8179,28 @@
         <v>39.16</v>
       </c>
       <c r="H24" t="n">
-        <v>22.18</v>
+        <v>13.19</v>
       </c>
       <c r="I24" t="n">
-        <v>58.83</v>
+        <v>69.25</v>
       </c>
       <c r="J24" t="n">
         <v>31.29</v>
       </c>
       <c r="K24" t="n">
-        <v>16.87</v>
+        <v>9.23</v>
       </c>
       <c r="L24" t="n">
-        <v>48.41</v>
+        <v>57.47</v>
       </c>
       <c r="M24" t="n">
         <v>23.42</v>
       </c>
       <c r="N24" t="n">
-        <v>11.55</v>
+        <v>5.27</v>
       </c>
       <c r="O24" t="n">
-        <v>37.98</v>
+        <v>45.69</v>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
@@ -8238,28 +8238,28 @@
         <v>38.54</v>
       </c>
       <c r="H25" t="n">
-        <v>22</v>
+        <v>13.24</v>
       </c>
       <c r="I25" t="n">
-        <v>57.92</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>30.28</v>
       </c>
       <c r="K25" t="n">
-        <v>16.35</v>
+        <v>8.98</v>
       </c>
       <c r="L25" t="n">
-        <v>47.05</v>
+        <v>55.92</v>
       </c>
       <c r="M25" t="n">
         <v>22.02</v>
       </c>
       <c r="N25" t="n">
-        <v>10.71</v>
+        <v>4.73</v>
       </c>
       <c r="O25" t="n">
-        <v>36.16</v>
+        <v>43.65</v>
       </c>
       <c r="P25" t="n">
         <v>20.6</v>
@@ -8301,28 +8301,28 @@
         <v>37.29</v>
       </c>
       <c r="H26" t="n">
-        <v>20.34</v>
+        <v>11.36</v>
       </c>
       <c r="I26" t="n">
-        <v>56.95</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>29.49</v>
       </c>
       <c r="K26" t="n">
-        <v>15.09</v>
+        <v>7.46</v>
       </c>
       <c r="L26" t="n">
-        <v>46.6</v>
+        <v>55.66</v>
       </c>
       <c r="M26" t="n">
         <v>21.7</v>
       </c>
       <c r="N26" t="n">
-        <v>9.83</v>
+        <v>3.55</v>
       </c>
       <c r="O26" t="n">
-        <v>36.26</v>
+        <v>43.97</v>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
@@ -8360,28 +8360,28 @@
         <v>36.95</v>
       </c>
       <c r="H27" t="n">
-        <v>21.09</v>
+        <v>12.7</v>
       </c>
       <c r="I27" t="n">
-        <v>55.77</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>29.08</v>
       </c>
       <c r="K27" t="n">
-        <v>15.78</v>
+        <v>8.74</v>
       </c>
       <c r="L27" t="n">
-        <v>45.35</v>
+        <v>53.96</v>
       </c>
       <c r="M27" t="n">
         <v>21.22</v>
       </c>
       <c r="N27" t="n">
-        <v>10.47</v>
+        <v>4.78</v>
       </c>
       <c r="O27" t="n">
-        <v>34.93</v>
+        <v>42.19</v>
       </c>
       <c r="P27" t="n">
         <v>22.3</v>
@@ -8423,28 +8423,28 @@
         <v>36.82</v>
       </c>
       <c r="H28" t="n">
-        <v>20.21</v>
+        <v>11.42</v>
       </c>
       <c r="I28" t="n">
-        <v>56.19</v>
+        <v>66.44</v>
       </c>
       <c r="J28" t="n">
         <v>29.38</v>
       </c>
       <c r="K28" t="n">
-        <v>15.26</v>
+        <v>7.78</v>
       </c>
       <c r="L28" t="n">
-        <v>46.26</v>
+        <v>55.2</v>
       </c>
       <c r="M28" t="n">
         <v>21.95</v>
       </c>
       <c r="N28" t="n">
-        <v>10.31</v>
+        <v>4.15</v>
       </c>
       <c r="O28" t="n">
-        <v>36.35</v>
+        <v>43.97</v>
       </c>
       <c r="P28" t="n">
         <v>17.3</v>
@@ -8486,28 +8486,28 @@
         <v>36.61</v>
       </c>
       <c r="H29" t="n">
-        <v>19.54</v>
+        <v>10.5</v>
       </c>
       <c r="I29" t="n">
-        <v>56.33</v>
+        <v>66.77</v>
       </c>
       <c r="J29" t="n">
         <v>29.01</v>
       </c>
       <c r="K29" t="n">
-        <v>14.45</v>
+        <v>6.74</v>
       </c>
       <c r="L29" t="n">
-        <v>46.22</v>
+        <v>55.33</v>
       </c>
       <c r="M29" t="n">
         <v>21.42</v>
       </c>
       <c r="N29" t="n">
-        <v>9.369999999999999</v>
+        <v>2.99</v>
       </c>
       <c r="O29" t="n">
-        <v>36.11</v>
+        <v>43.89</v>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
@@ -8545,28 +8545,28 @@
         <v>36.04</v>
       </c>
       <c r="H30" t="n">
-        <v>19.73</v>
+        <v>11.09</v>
       </c>
       <c r="I30" t="n">
-        <v>55.21</v>
+        <v>65.36</v>
       </c>
       <c r="J30" t="n">
         <v>28.52</v>
       </c>
       <c r="K30" t="n">
-        <v>14.7</v>
+        <v>7.38</v>
       </c>
       <c r="L30" t="n">
-        <v>45.19</v>
+        <v>54.01</v>
       </c>
       <c r="M30" t="n">
         <v>20.99</v>
       </c>
       <c r="N30" t="n">
-        <v>9.67</v>
+        <v>3.68</v>
       </c>
       <c r="O30" t="n">
-        <v>35.16</v>
+        <v>42.66</v>
       </c>
       <c r="P30" t="n">
         <v>35.1</v>
@@ -8608,28 +8608,28 @@
         <v>35.15</v>
       </c>
       <c r="H31" t="n">
-        <v>18.69</v>
+        <v>9.98</v>
       </c>
       <c r="I31" t="n">
-        <v>54.43</v>
+        <v>64.64</v>
       </c>
       <c r="J31" t="n">
         <v>27.48</v>
       </c>
       <c r="K31" t="n">
-        <v>13.55</v>
+        <v>6.18</v>
       </c>
       <c r="L31" t="n">
-        <v>44.25</v>
+        <v>53.12</v>
       </c>
       <c r="M31" t="n">
         <v>19.82</v>
       </c>
       <c r="N31" t="n">
-        <v>8.41</v>
+        <v>2.37</v>
       </c>
       <c r="O31" t="n">
-        <v>34.05</v>
+        <v>41.59</v>
       </c>
       <c r="P31" t="n">
         <v>30.7</v>
@@ -8671,28 +8671,28 @@
         <v>33.81</v>
       </c>
       <c r="H32" t="n">
-        <v>17.62</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>52.81</v>
+        <v>62.87</v>
       </c>
       <c r="J32" t="n">
         <v>26.9</v>
       </c>
       <c r="K32" t="n">
-        <v>13.11</v>
+        <v>5.81</v>
       </c>
       <c r="L32" t="n">
-        <v>43.51</v>
+        <v>52.3</v>
       </c>
       <c r="M32" t="n">
         <v>19.99</v>
       </c>
       <c r="N32" t="n">
-        <v>8.59</v>
+        <v>2.56</v>
       </c>
       <c r="O32" t="n">
-        <v>34.2</v>
+        <v>41.72</v>
       </c>
       <c r="P32" t="n">
         <v>23</v>
@@ -8734,28 +8734,28 @@
         <v>21.16</v>
       </c>
       <c r="H33" t="n">
-        <v>8.91</v>
+        <v>2.43</v>
       </c>
       <c r="I33" t="n">
-        <v>36.58</v>
+        <v>44.74</v>
       </c>
       <c r="J33" t="n">
         <v>17.47</v>
       </c>
       <c r="K33" t="n">
-        <v>6.98</v>
+        <v>1.42</v>
       </c>
       <c r="L33" t="n">
-        <v>31.14</v>
+        <v>38.38</v>
       </c>
       <c r="M33" t="n">
         <v>13.79</v>
       </c>
       <c r="N33" t="n">
-        <v>5.04</v>
+        <v>0.41</v>
       </c>
       <c r="O33" t="n">
-        <v>25.7</v>
+        <v>32.01</v>
       </c>
       <c r="P33" t="n">
         <v>9.9</v>

--- a/projections/te_2026_combined.xlsx
+++ b/projections/te_2026_combined.xlsx
@@ -567,10 +567,10 @@
         <v>200</v>
       </c>
       <c r="P2" t="n">
-        <v>252.3</v>
+        <v>264</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.99</v>
+        <v>-16.69</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -630,10 +630,10 @@
         <v>193.03</v>
       </c>
       <c r="P3" t="n">
-        <v>240.1</v>
+        <v>246</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.4</v>
+        <v>-3.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -693,10 +693,10 @@
         <v>205.47</v>
       </c>
       <c r="P4" t="n">
-        <v>175.3</v>
+        <v>198</v>
       </c>
       <c r="Q4" t="n">
-        <v>62.15</v>
+        <v>39.45</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -756,10 +756,10 @@
         <v>181.94</v>
       </c>
       <c r="P5" t="n">
-        <v>256.3</v>
+        <v>269</v>
       </c>
       <c r="Q5" t="n">
-        <v>-36.44</v>
+        <v>-49.14</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         <v>174.37</v>
       </c>
       <c r="P6" t="n">
-        <v>187.3</v>
+        <v>200</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.91</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>172.74</v>
       </c>
       <c r="P7" t="n">
-        <v>197.5</v>
+        <v>207</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.02</v>
+        <v>-12.52</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         <v>150.35</v>
       </c>
       <c r="P8" t="n">
-        <v>221.2</v>
+        <v>229</v>
       </c>
       <c r="Q8" t="n">
-        <v>-26.8</v>
+        <v>-34.6</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>157.02</v>
       </c>
       <c r="P9" t="n">
-        <v>195.2</v>
+        <v>208</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.18</v>
+        <v>-16.98</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
         <v>169.8</v>
       </c>
       <c r="P10" t="n">
-        <v>210.6</v>
+        <v>208</v>
       </c>
       <c r="Q10" t="n">
-        <v>-26.23</v>
+        <v>-23.63</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         <v>154.07</v>
       </c>
       <c r="P11" t="n">
-        <v>184.8</v>
+        <v>189</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.18</v>
+        <v>-6.38</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1197,10 +1197,10 @@
         <v>154.61</v>
       </c>
       <c r="P12" t="n">
-        <v>161.6</v>
+        <v>172</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.28</v>
+        <v>0.88</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
         <v>144.88</v>
       </c>
       <c r="P13" t="n">
-        <v>154.4</v>
+        <v>166</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.63</v>
+        <v>4.03</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1323,10 +1323,10 @@
         <v>143.56</v>
       </c>
       <c r="P14" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.75</v>
+        <v>12.75</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1386,10 +1386,10 @@
         <v>148.43</v>
       </c>
       <c r="P15" t="n">
-        <v>155.1</v>
+        <v>160</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.859999999999999</v>
+        <v>3.96</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         <v>134.78</v>
       </c>
       <c r="P16" t="n">
-        <v>132.6</v>
+        <v>146</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.49</v>
+        <v>8.09</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -1512,10 +1512,10 @@
         <v>138.43</v>
       </c>
       <c r="P17" t="n">
-        <v>161.2</v>
+        <v>167</v>
       </c>
       <c r="Q17" t="n">
-        <v>-7.99</v>
+        <v>-13.79</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -1575,10 +1575,10 @@
         <v>134.07</v>
       </c>
       <c r="P18" t="n">
-        <v>160.9</v>
+        <v>175</v>
       </c>
       <c r="Q18" t="n">
-        <v>-20.01</v>
+        <v>-34.11</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
         <v>123.48</v>
       </c>
       <c r="P19" t="n">
-        <v>147.8</v>
+        <v>153</v>
       </c>
       <c r="Q19" t="n">
-        <v>-7.76</v>
+        <v>-12.96</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
         <v>121.53</v>
       </c>
       <c r="P20" t="n">
-        <v>67.5</v>
+        <v>100</v>
       </c>
       <c r="Q20" t="n">
-        <v>70.48999999999999</v>
+        <v>37.99</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
         <v>120.23</v>
       </c>
       <c r="P21" t="n">
-        <v>139.3</v>
+        <v>154</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.99</v>
+        <v>-19.69</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -1827,10 +1827,10 @@
         <v>125.37</v>
       </c>
       <c r="P22" t="n">
-        <v>156.8</v>
+        <v>170</v>
       </c>
       <c r="Q22" t="n">
-        <v>-23.93</v>
+        <v>-37.13</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         <v>123.27</v>
       </c>
       <c r="P23" t="n">
-        <v>125.3</v>
+        <v>144</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.27</v>
+        <v>-11.43</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         <v>122.86</v>
       </c>
       <c r="P24" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.97</v>
+        <v>-7.03</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2016,10 +2016,10 @@
         <v>122.16</v>
       </c>
       <c r="P25" t="n">
-        <v>106.4</v>
+        <v>125</v>
       </c>
       <c r="Q25" t="n">
-        <v>25.43</v>
+        <v>6.83</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         <v>120.61</v>
       </c>
       <c r="P26" t="n">
-        <v>105.8</v>
+        <v>128</v>
       </c>
       <c r="Q26" t="n">
-        <v>24.74</v>
+        <v>2.54</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>119.75</v>
       </c>
       <c r="P27" t="n">
-        <v>104.7</v>
+        <v>131</v>
       </c>
       <c r="Q27" t="n">
-        <v>25.39</v>
+        <v>-0.91</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -2205,10 +2205,10 @@
         <v>113.22</v>
       </c>
       <c r="P28" t="n">
-        <v>152.8</v>
+        <v>168</v>
       </c>
       <c r="Q28" t="n">
-        <v>-23.37</v>
+        <v>-38.57</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -2268,10 +2268,10 @@
         <v>107.89</v>
       </c>
       <c r="P29" t="n">
-        <v>166.6</v>
+        <v>171</v>
       </c>
       <c r="Q29" t="n">
-        <v>-42.85</v>
+        <v>-47.25</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
         <v>114.2</v>
       </c>
       <c r="P30" t="n">
-        <v>109.1</v>
+        <v>124</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.470000000000001</v>
+        <v>-5.43</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
         <v>98.48</v>
       </c>
       <c r="P31" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="Q31" t="n">
-        <v>-24.37</v>
+        <v>-29.37</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -2457,10 +2457,10 @@
         <v>95.15000000000001</v>
       </c>
       <c r="P32" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="Q32" t="n">
-        <v>43.95</v>
+        <v>27.95</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         <v>78.91</v>
       </c>
       <c r="P33" t="n">
-        <v>54.4</v>
+        <v>127</v>
       </c>
       <c r="Q33" t="n">
-        <v>14.54</v>
+        <v>-58.06</v>
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         <v>77.84</v>
       </c>
       <c r="P34" t="n">
-        <v>148.6</v>
+        <v>155</v>
       </c>
       <c r="Q34" t="n">
-        <v>-60.1</v>
+        <v>-66.5</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -2642,10 +2642,10 @@
         <v>81.37</v>
       </c>
       <c r="P35" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="Q35" t="n">
-        <v>26.56</v>
+        <v>4.56</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -2705,10 +2705,10 @@
         <v>80.20999999999999</v>
       </c>
       <c r="P36" t="n">
-        <v>113.9</v>
+        <v>112</v>
       </c>
       <c r="Q36" t="n">
-        <v>-33.84</v>
+        <v>-31.94</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -2768,10 +2768,10 @@
         <v>70.40000000000001</v>
       </c>
       <c r="P37" t="n">
-        <v>99.3</v>
+        <v>121</v>
       </c>
       <c r="Q37" t="n">
-        <v>-22.69</v>
+        <v>-44.39</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>66.64</v>
       </c>
       <c r="P38" t="n">
-        <v>84.59999999999999</v>
+        <v>116</v>
       </c>
       <c r="Q38" t="n">
-        <v>-10.17</v>
+        <v>-41.57</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -2894,10 +2894,10 @@
         <v>69.34999999999999</v>
       </c>
       <c r="P39" t="n">
-        <v>60.5</v>
+        <v>80</v>
       </c>
       <c r="Q39" t="n">
-        <v>11.72</v>
+        <v>-7.78</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -2957,10 +2957,10 @@
         <v>69.39</v>
       </c>
       <c r="P40" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.89</v>
+        <v>-19.11</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -3020,10 +3020,10 @@
         <v>56.23</v>
       </c>
       <c r="P41" t="n">
-        <v>69.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="Q41" t="n">
-        <v>-14.63</v>
+        <v>-33.53</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -3083,10 +3083,10 @@
         <v>53.25</v>
       </c>
       <c r="P42" t="n">
-        <v>43.9</v>
+        <v>76</v>
       </c>
       <c r="Q42" t="n">
-        <v>7.12</v>
+        <v>-24.98</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -3146,10 +3146,10 @@
         <v>50.69</v>
       </c>
       <c r="P43" t="n">
-        <v>45.9</v>
+        <v>67</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.76</v>
+        <v>-17.34</v>
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         <v>49.73</v>
       </c>
       <c r="P44" t="n">
-        <v>63.8</v>
+        <v>84</v>
       </c>
       <c r="Q44" t="n">
-        <v>-17.22</v>
+        <v>-37.42</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -3268,10 +3268,10 @@
         <v>53.12</v>
       </c>
       <c r="P45" t="n">
-        <v>22.3</v>
+        <v>53</v>
       </c>
       <c r="Q45" t="n">
-        <v>24.11</v>
+        <v>-6.59</v>
       </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
@@ -3327,10 +3327,10 @@
         <v>49.27</v>
       </c>
       <c r="P46" t="n">
-        <v>71.59999999999999</v>
+        <v>55</v>
       </c>
       <c r="Q46" t="n">
-        <v>-26.44</v>
+        <v>-9.84</v>
       </c>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -3386,10 +3386,10 @@
         <v>50.8</v>
       </c>
       <c r="P47" t="n">
-        <v>33.2</v>
+        <v>55</v>
       </c>
       <c r="Q47" t="n">
-        <v>11.59</v>
+        <v>-10.21</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -3449,10 +3449,10 @@
         <v>47.54</v>
       </c>
       <c r="P48" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="Q48" t="n">
-        <v>-16.56</v>
+        <v>-40.56</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -3512,10 +3512,10 @@
         <v>47.95</v>
       </c>
       <c r="P49" t="n">
-        <v>55.2</v>
+        <v>66</v>
       </c>
       <c r="Q49" t="n">
-        <v>-11.63</v>
+        <v>-22.43</v>
       </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         <v>49.76</v>
       </c>
       <c r="P50" t="n">
-        <v>44.4</v>
+        <v>90</v>
       </c>
       <c r="Q50" t="n">
-        <v>-2.08</v>
+        <v>-47.68</v>
       </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
@@ -3630,10 +3630,10 @@
         <v>47.08</v>
       </c>
       <c r="P51" t="n">
-        <v>36.6</v>
+        <v>54</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.69</v>
+        <v>-11.71</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         <v>49.38</v>
       </c>
       <c r="P52" t="n">
-        <v>43.9</v>
+        <v>71</v>
       </c>
       <c r="Q52" t="n">
-        <v>-1.74</v>
+        <v>-28.84</v>
       </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         <v>48.92</v>
       </c>
       <c r="P53" t="n">
-        <v>30.2</v>
+        <v>52</v>
       </c>
       <c r="Q53" t="n">
-        <v>11.71</v>
+        <v>-10.09</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -3815,10 +3815,10 @@
         <v>47.42</v>
       </c>
       <c r="P54" t="n">
-        <v>34.9</v>
+        <v>50</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.92</v>
+        <v>-8.18</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -3878,10 +3878,10 @@
         <v>47.02</v>
       </c>
       <c r="P55" t="n">
-        <v>49.8</v>
+        <v>55</v>
       </c>
       <c r="Q55" t="n">
-        <v>-9.52</v>
+        <v>-14.72</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -3940,8 +3940,12 @@
       <c r="O56" t="n">
         <v>46.05</v>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>-26.97</v>
+      </c>
       <c r="R56" t="inlineStr">
         <is>
           <t>50</t>
@@ -4118,10 +4122,10 @@
         <v>44.81</v>
       </c>
       <c r="P59" t="n">
-        <v>19.8</v>
+        <v>26</v>
       </c>
       <c r="Q59" t="n">
-        <v>16.54</v>
+        <v>10.34</v>
       </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
@@ -4177,10 +4181,10 @@
         <v>41.35</v>
       </c>
       <c r="P60" t="n">
-        <v>30.7</v>
+        <v>53</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.86</v>
+        <v>-17.44</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -4295,10 +4299,10 @@
         <v>42.05</v>
       </c>
       <c r="P62" t="n">
-        <v>22.3</v>
+        <v>37</v>
       </c>
       <c r="Q62" t="n">
-        <v>12.68</v>
+        <v>-2.02</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -4358,10 +4362,10 @@
         <v>42.95</v>
       </c>
       <c r="P63" t="n">
-        <v>17.3</v>
+        <v>28</v>
       </c>
       <c r="Q63" t="n">
-        <v>17.44</v>
+        <v>6.74</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -4421,10 +4425,10 @@
         <v>39.72</v>
       </c>
       <c r="P64" t="n">
-        <v>20.3</v>
+        <v>32</v>
       </c>
       <c r="Q64" t="n">
-        <v>12.63</v>
+        <v>0.93</v>
       </c>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
@@ -4480,10 +4484,10 @@
         <v>28.42</v>
       </c>
       <c r="P65" t="n">
-        <v>9.9</v>
+        <v>12</v>
       </c>
       <c r="Q65" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -4654,10 +4658,10 @@
         <v>200</v>
       </c>
       <c r="P2" t="n">
-        <v>252.3</v>
+        <v>264</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.99</v>
+        <v>-16.69</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -4717,10 +4721,10 @@
         <v>193.03</v>
       </c>
       <c r="P3" t="n">
-        <v>240.1</v>
+        <v>246</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.4</v>
+        <v>-3.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -4780,10 +4784,10 @@
         <v>205.47</v>
       </c>
       <c r="P4" t="n">
-        <v>175.3</v>
+        <v>198</v>
       </c>
       <c r="Q4" t="n">
-        <v>62.15</v>
+        <v>39.45</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -4843,10 +4847,10 @@
         <v>181.94</v>
       </c>
       <c r="P5" t="n">
-        <v>256.3</v>
+        <v>269</v>
       </c>
       <c r="Q5" t="n">
-        <v>-36.44</v>
+        <v>-49.14</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -4906,10 +4910,10 @@
         <v>174.37</v>
       </c>
       <c r="P6" t="n">
-        <v>187.3</v>
+        <v>200</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.91</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -4969,10 +4973,10 @@
         <v>172.74</v>
       </c>
       <c r="P7" t="n">
-        <v>197.5</v>
+        <v>207</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.02</v>
+        <v>-12.52</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -5032,10 +5036,10 @@
         <v>150.35</v>
       </c>
       <c r="P8" t="n">
-        <v>221.2</v>
+        <v>229</v>
       </c>
       <c r="Q8" t="n">
-        <v>-26.8</v>
+        <v>-34.6</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -5095,10 +5099,10 @@
         <v>157.02</v>
       </c>
       <c r="P9" t="n">
-        <v>195.2</v>
+        <v>208</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.18</v>
+        <v>-16.98</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -5158,10 +5162,10 @@
         <v>169.8</v>
       </c>
       <c r="P10" t="n">
-        <v>210.6</v>
+        <v>208</v>
       </c>
       <c r="Q10" t="n">
-        <v>-26.23</v>
+        <v>-23.63</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -5221,10 +5225,10 @@
         <v>154.07</v>
       </c>
       <c r="P11" t="n">
-        <v>184.8</v>
+        <v>189</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.18</v>
+        <v>-6.38</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -5284,10 +5288,10 @@
         <v>154.61</v>
       </c>
       <c r="P12" t="n">
-        <v>161.6</v>
+        <v>172</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.28</v>
+        <v>0.88</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -5347,10 +5351,10 @@
         <v>144.88</v>
       </c>
       <c r="P13" t="n">
-        <v>154.4</v>
+        <v>166</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.63</v>
+        <v>4.03</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -5410,10 +5414,10 @@
         <v>143.56</v>
       </c>
       <c r="P14" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.75</v>
+        <v>12.75</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -5473,10 +5477,10 @@
         <v>148.43</v>
       </c>
       <c r="P15" t="n">
-        <v>155.1</v>
+        <v>160</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.859999999999999</v>
+        <v>3.96</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -5536,10 +5540,10 @@
         <v>134.78</v>
       </c>
       <c r="P16" t="n">
-        <v>132.6</v>
+        <v>146</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.49</v>
+        <v>8.09</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -5599,10 +5603,10 @@
         <v>138.43</v>
       </c>
       <c r="P17" t="n">
-        <v>161.2</v>
+        <v>167</v>
       </c>
       <c r="Q17" t="n">
-        <v>-7.99</v>
+        <v>-13.79</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -5662,10 +5666,10 @@
         <v>134.07</v>
       </c>
       <c r="P18" t="n">
-        <v>160.9</v>
+        <v>175</v>
       </c>
       <c r="Q18" t="n">
-        <v>-20.01</v>
+        <v>-34.11</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -5725,10 +5729,10 @@
         <v>123.48</v>
       </c>
       <c r="P19" t="n">
-        <v>147.8</v>
+        <v>153</v>
       </c>
       <c r="Q19" t="n">
-        <v>-7.76</v>
+        <v>-12.96</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -5788,10 +5792,10 @@
         <v>121.53</v>
       </c>
       <c r="P20" t="n">
-        <v>67.5</v>
+        <v>100</v>
       </c>
       <c r="Q20" t="n">
-        <v>70.48999999999999</v>
+        <v>37.99</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -5851,10 +5855,10 @@
         <v>120.23</v>
       </c>
       <c r="P21" t="n">
-        <v>139.3</v>
+        <v>154</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.99</v>
+        <v>-19.69</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -5914,10 +5918,10 @@
         <v>125.37</v>
       </c>
       <c r="P22" t="n">
-        <v>156.8</v>
+        <v>170</v>
       </c>
       <c r="Q22" t="n">
-        <v>-23.93</v>
+        <v>-37.13</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -5977,10 +5981,10 @@
         <v>123.27</v>
       </c>
       <c r="P23" t="n">
-        <v>125.3</v>
+        <v>144</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.27</v>
+        <v>-11.43</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -6040,10 +6044,10 @@
         <v>122.86</v>
       </c>
       <c r="P24" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.97</v>
+        <v>-7.03</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -6103,10 +6107,10 @@
         <v>122.16</v>
       </c>
       <c r="P25" t="n">
-        <v>106.4</v>
+        <v>125</v>
       </c>
       <c r="Q25" t="n">
-        <v>25.43</v>
+        <v>6.83</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -6166,10 +6170,10 @@
         <v>120.61</v>
       </c>
       <c r="P26" t="n">
-        <v>105.8</v>
+        <v>128</v>
       </c>
       <c r="Q26" t="n">
-        <v>24.74</v>
+        <v>2.54</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -6229,10 +6233,10 @@
         <v>119.75</v>
       </c>
       <c r="P27" t="n">
-        <v>104.7</v>
+        <v>131</v>
       </c>
       <c r="Q27" t="n">
-        <v>25.39</v>
+        <v>-0.91</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -6292,10 +6296,10 @@
         <v>113.22</v>
       </c>
       <c r="P28" t="n">
-        <v>152.8</v>
+        <v>168</v>
       </c>
       <c r="Q28" t="n">
-        <v>-23.37</v>
+        <v>-38.57</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -6355,10 +6359,10 @@
         <v>107.89</v>
       </c>
       <c r="P29" t="n">
-        <v>166.6</v>
+        <v>171</v>
       </c>
       <c r="Q29" t="n">
-        <v>-42.85</v>
+        <v>-47.25</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -6418,10 +6422,10 @@
         <v>114.2</v>
       </c>
       <c r="P30" t="n">
-        <v>109.1</v>
+        <v>124</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.470000000000001</v>
+        <v>-5.43</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -6481,10 +6485,10 @@
         <v>98.48</v>
       </c>
       <c r="P31" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="Q31" t="n">
-        <v>-24.37</v>
+        <v>-29.37</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -6544,10 +6548,10 @@
         <v>95.15000000000001</v>
       </c>
       <c r="P32" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="Q32" t="n">
-        <v>43.95</v>
+        <v>27.95</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -6607,10 +6611,10 @@
         <v>78.91</v>
       </c>
       <c r="P33" t="n">
-        <v>54.4</v>
+        <v>127</v>
       </c>
       <c r="Q33" t="n">
-        <v>14.54</v>
+        <v>-58.06</v>
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -6777,10 +6781,10 @@
         <v>77.84</v>
       </c>
       <c r="P2" t="n">
-        <v>148.6</v>
+        <v>155</v>
       </c>
       <c r="Q2" t="n">
-        <v>-60.1</v>
+        <v>-66.5</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -6840,10 +6844,10 @@
         <v>81.37</v>
       </c>
       <c r="P3" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="Q3" t="n">
-        <v>26.56</v>
+        <v>4.56</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -6903,10 +6907,10 @@
         <v>80.20999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>113.9</v>
+        <v>112</v>
       </c>
       <c r="Q4" t="n">
-        <v>-33.84</v>
+        <v>-31.94</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -6966,10 +6970,10 @@
         <v>70.40000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>99.3</v>
+        <v>121</v>
       </c>
       <c r="Q5" t="n">
-        <v>-22.69</v>
+        <v>-44.39</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -7029,10 +7033,10 @@
         <v>66.64</v>
       </c>
       <c r="P6" t="n">
-        <v>84.59999999999999</v>
+        <v>116</v>
       </c>
       <c r="Q6" t="n">
-        <v>-10.17</v>
+        <v>-41.57</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -7092,10 +7096,10 @@
         <v>69.34999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>60.5</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.72</v>
+        <v>-7.78</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -7155,10 +7159,10 @@
         <v>69.39</v>
       </c>
       <c r="P8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.89</v>
+        <v>-19.11</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -7218,10 +7222,10 @@
         <v>56.23</v>
       </c>
       <c r="P9" t="n">
-        <v>69.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="Q9" t="n">
-        <v>-14.63</v>
+        <v>-33.53</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -7281,10 +7285,10 @@
         <v>53.25</v>
       </c>
       <c r="P10" t="n">
-        <v>43.9</v>
+        <v>76</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.12</v>
+        <v>-24.98</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -7344,10 +7348,10 @@
         <v>50.69</v>
       </c>
       <c r="P11" t="n">
-        <v>45.9</v>
+        <v>67</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.76</v>
+        <v>-17.34</v>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -7403,10 +7407,10 @@
         <v>49.73</v>
       </c>
       <c r="P12" t="n">
-        <v>63.8</v>
+        <v>84</v>
       </c>
       <c r="Q12" t="n">
-        <v>-17.22</v>
+        <v>-37.42</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -7466,10 +7470,10 @@
         <v>53.12</v>
       </c>
       <c r="P13" t="n">
-        <v>22.3</v>
+        <v>53</v>
       </c>
       <c r="Q13" t="n">
-        <v>24.11</v>
+        <v>-6.59</v>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -7525,10 +7529,10 @@
         <v>49.27</v>
       </c>
       <c r="P14" t="n">
-        <v>71.59999999999999</v>
+        <v>55</v>
       </c>
       <c r="Q14" t="n">
-        <v>-26.44</v>
+        <v>-9.84</v>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -7584,10 +7588,10 @@
         <v>50.8</v>
       </c>
       <c r="P15" t="n">
-        <v>33.2</v>
+        <v>55</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.59</v>
+        <v>-10.21</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -7647,10 +7651,10 @@
         <v>47.54</v>
       </c>
       <c r="P16" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="Q16" t="n">
-        <v>-16.56</v>
+        <v>-40.56</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -7710,10 +7714,10 @@
         <v>47.95</v>
       </c>
       <c r="P17" t="n">
-        <v>55.2</v>
+        <v>66</v>
       </c>
       <c r="Q17" t="n">
-        <v>-11.63</v>
+        <v>-22.43</v>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
@@ -7769,10 +7773,10 @@
         <v>49.76</v>
       </c>
       <c r="P18" t="n">
-        <v>44.4</v>
+        <v>90</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.08</v>
+        <v>-47.68</v>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -7828,10 +7832,10 @@
         <v>47.08</v>
       </c>
       <c r="P19" t="n">
-        <v>36.6</v>
+        <v>54</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.69</v>
+        <v>-11.71</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -7891,10 +7895,10 @@
         <v>49.38</v>
       </c>
       <c r="P20" t="n">
-        <v>43.9</v>
+        <v>71</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.74</v>
+        <v>-28.84</v>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -7950,10 +7954,10 @@
         <v>48.92</v>
       </c>
       <c r="P21" t="n">
-        <v>30.2</v>
+        <v>52</v>
       </c>
       <c r="Q21" t="n">
-        <v>11.71</v>
+        <v>-10.09</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -8013,10 +8017,10 @@
         <v>47.42</v>
       </c>
       <c r="P22" t="n">
-        <v>34.9</v>
+        <v>50</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.92</v>
+        <v>-8.18</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -8076,10 +8080,10 @@
         <v>47.02</v>
       </c>
       <c r="P23" t="n">
-        <v>49.8</v>
+        <v>55</v>
       </c>
       <c r="Q23" t="n">
-        <v>-9.52</v>
+        <v>-14.72</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -8138,8 +8142,12 @@
       <c r="O24" t="n">
         <v>46.05</v>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-26.97</v>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
           <t>50</t>
@@ -8316,10 +8324,10 @@
         <v>44.81</v>
       </c>
       <c r="P27" t="n">
-        <v>19.8</v>
+        <v>26</v>
       </c>
       <c r="Q27" t="n">
-        <v>16.54</v>
+        <v>10.34</v>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
@@ -8375,10 +8383,10 @@
         <v>41.35</v>
       </c>
       <c r="P28" t="n">
-        <v>30.7</v>
+        <v>53</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.86</v>
+        <v>-17.44</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -8493,10 +8501,10 @@
         <v>42.05</v>
       </c>
       <c r="P30" t="n">
-        <v>22.3</v>
+        <v>37</v>
       </c>
       <c r="Q30" t="n">
-        <v>12.68</v>
+        <v>-2.02</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -8556,10 +8564,10 @@
         <v>42.95</v>
       </c>
       <c r="P31" t="n">
-        <v>17.3</v>
+        <v>28</v>
       </c>
       <c r="Q31" t="n">
-        <v>17.44</v>
+        <v>6.74</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -8619,10 +8627,10 @@
         <v>39.72</v>
       </c>
       <c r="P32" t="n">
-        <v>20.3</v>
+        <v>32</v>
       </c>
       <c r="Q32" t="n">
-        <v>12.63</v>
+        <v>0.93</v>
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -8678,10 +8686,10 @@
         <v>28.42</v>
       </c>
       <c r="P33" t="n">
-        <v>9.9</v>
+        <v>12</v>
       </c>
       <c r="Q33" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>

--- a/projections/te_2026_combined.xlsx
+++ b/projections/te_2026_combined.xlsx
@@ -567,16 +567,12 @@
         <v>200</v>
       </c>
       <c r="P2" t="n">
-        <v>264</v>
+        <v>253.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>-16.69</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+        <v>-5.99</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -630,16 +626,12 @@
         <v>193.03</v>
       </c>
       <c r="P3" t="n">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -693,16 +685,12 @@
         <v>205.47</v>
       </c>
       <c r="P4" t="n">
-        <v>198</v>
+        <v>185.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>39.45</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>51.65</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -756,16 +744,12 @@
         <v>181.94</v>
       </c>
       <c r="P5" t="n">
-        <v>269</v>
+        <v>260.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>-49.14</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>-40.24</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -819,16 +803,12 @@
         <v>174.37</v>
       </c>
       <c r="P6" t="n">
-        <v>200</v>
+        <v>187.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+        <v>21.91</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -882,16 +862,12 @@
         <v>172.74</v>
       </c>
       <c r="P7" t="n">
-        <v>207</v>
+        <v>197.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>-12.52</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+        <v>-3.02</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -945,16 +921,12 @@
         <v>150.35</v>
       </c>
       <c r="P8" t="n">
-        <v>229</v>
+        <v>225.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>-34.6</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+        <v>-31</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1008,16 +980,12 @@
         <v>157.02</v>
       </c>
       <c r="P9" t="n">
-        <v>208</v>
+        <v>202.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>-16.98</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>-11.78</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1071,16 +1039,12 @@
         <v>169.8</v>
       </c>
       <c r="P10" t="n">
-        <v>208</v>
+        <v>195.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>-23.63</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+        <v>-11.23</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1134,16 +1098,12 @@
         <v>154.07</v>
       </c>
       <c r="P11" t="n">
-        <v>189</v>
+        <v>184.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.38</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+        <v>-1.98</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1197,16 +1157,12 @@
         <v>154.61</v>
       </c>
       <c r="P12" t="n">
-        <v>172</v>
+        <v>163.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+        <v>9.48</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1260,16 +1216,12 @@
         <v>144.88</v>
       </c>
       <c r="P13" t="n">
-        <v>166</v>
+        <v>160.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+        <v>9.73</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1323,16 +1275,12 @@
         <v>143.56</v>
       </c>
       <c r="P14" t="n">
-        <v>156</v>
+        <v>151.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+        <v>16.95</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1386,16 +1334,12 @@
         <v>148.43</v>
       </c>
       <c r="P15" t="n">
-        <v>160</v>
+        <v>146.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+        <v>17.26</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1449,16 +1393,12 @@
         <v>134.78</v>
       </c>
       <c r="P16" t="n">
-        <v>146</v>
+        <v>132.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>21.39</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1512,16 +1452,12 @@
         <v>138.43</v>
       </c>
       <c r="P17" t="n">
-        <v>167</v>
+        <v>160.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>-13.79</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>-7.59</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1575,16 +1511,12 @@
         <v>134.07</v>
       </c>
       <c r="P18" t="n">
-        <v>175</v>
+        <v>160.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>-34.11</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+        <v>-20.01</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1638,16 +1570,12 @@
         <v>123.48</v>
       </c>
       <c r="P19" t="n">
-        <v>153</v>
+        <v>147.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>-12.96</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+        <v>-7.76</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1701,16 +1629,12 @@
         <v>121.53</v>
       </c>
       <c r="P20" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>37.99</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>66.59</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1764,16 +1688,12 @@
         <v>120.23</v>
       </c>
       <c r="P21" t="n">
-        <v>154</v>
+        <v>140.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>-19.69</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+        <v>-5.89</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1827,16 +1747,12 @@
         <v>125.37</v>
       </c>
       <c r="P22" t="n">
-        <v>170</v>
+        <v>163.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>-37.13</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>-30.33</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1890,16 +1806,12 @@
         <v>123.27</v>
       </c>
       <c r="P23" t="n">
-        <v>144</v>
+        <v>125.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>-11.43</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>7.27</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1953,16 +1865,12 @@
         <v>122.86</v>
       </c>
       <c r="P24" t="n">
-        <v>139</v>
+        <v>123.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>-7.03</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>8.17</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2016,16 +1924,12 @@
         <v>122.16</v>
       </c>
       <c r="P25" t="n">
-        <v>125</v>
+        <v>106.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>25.43</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2079,16 +1983,12 @@
         <v>120.61</v>
       </c>
       <c r="P26" t="n">
-        <v>128</v>
+        <v>110.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+        <v>20.34</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2142,16 +2042,12 @@
         <v>119.75</v>
       </c>
       <c r="P27" t="n">
-        <v>131</v>
+        <v>115.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+        <v>14.49</v>
+      </c>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2205,16 +2101,12 @@
         <v>113.22</v>
       </c>
       <c r="P28" t="n">
-        <v>168</v>
+        <v>157.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>-38.57</v>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>-27.87</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2268,16 +2160,12 @@
         <v>107.89</v>
       </c>
       <c r="P29" t="n">
-        <v>171</v>
+        <v>166.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>-47.25</v>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+        <v>-42.85</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2331,16 +2219,12 @@
         <v>114.2</v>
       </c>
       <c r="P30" t="n">
-        <v>124</v>
+        <v>108.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>-5.43</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>9.67</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2394,16 +2278,12 @@
         <v>98.48</v>
       </c>
       <c r="P31" t="n">
-        <v>133</v>
+        <v>121.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>-29.37</v>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+        <v>-17.97</v>
+      </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2457,16 +2337,12 @@
         <v>95.15000000000001</v>
       </c>
       <c r="P32" t="n">
-        <v>64</v>
+        <v>38.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>27.95</v>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>53.65</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2520,10 +2396,10 @@
         <v>78.91</v>
       </c>
       <c r="P33" t="n">
-        <v>127</v>
+        <v>107.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>-58.06</v>
+        <v>-38.66</v>
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -2579,16 +2455,12 @@
         <v>77.84</v>
       </c>
       <c r="P34" t="n">
-        <v>155</v>
+        <v>140.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>-66.5</v>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>-51.8</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2642,16 +2514,12 @@
         <v>81.37</v>
       </c>
       <c r="P35" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+        <v>26.56</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2705,16 +2573,12 @@
         <v>80.20999999999999</v>
       </c>
       <c r="P36" t="n">
-        <v>112</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Q36" t="n">
-        <v>-31.94</v>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>-4.84</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2768,16 +2632,12 @@
         <v>70.40000000000001</v>
       </c>
       <c r="P37" t="n">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="Q37" t="n">
-        <v>-44.39</v>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+        <v>-23.39</v>
+      </c>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2831,16 +2691,12 @@
         <v>66.64</v>
       </c>
       <c r="P38" t="n">
-        <v>116</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="Q38" t="n">
-        <v>-41.57</v>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+        <v>-20.47</v>
+      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2894,16 +2750,12 @@
         <v>69.34999999999999</v>
       </c>
       <c r="P39" t="n">
-        <v>80</v>
+        <v>56.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>-7.78</v>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>15.82</v>
+      </c>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -2957,16 +2809,12 @@
         <v>69.39</v>
       </c>
       <c r="P40" t="n">
-        <v>90</v>
+        <v>69.7</v>
       </c>
       <c r="Q40" t="n">
-        <v>-19.11</v>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+        <v>1.19</v>
+      </c>
+      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -3020,16 +2868,12 @@
         <v>56.23</v>
       </c>
       <c r="P41" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="Q41" t="n">
-        <v>-33.53</v>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+        <v>-10.53</v>
+      </c>
+      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -3083,16 +2927,12 @@
         <v>53.25</v>
       </c>
       <c r="P42" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="Q42" t="n">
-        <v>-24.98</v>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -3146,10 +2986,10 @@
         <v>50.69</v>
       </c>
       <c r="P43" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="Q43" t="n">
-        <v>-17.34</v>
+        <v>5.66</v>
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -3205,16 +3045,12 @@
         <v>49.73</v>
       </c>
       <c r="P44" t="n">
-        <v>84</v>
+        <v>63.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>-37.42</v>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+        <v>-17.22</v>
+      </c>
+      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3268,10 +3104,10 @@
         <v>53.12</v>
       </c>
       <c r="P45" t="n">
-        <v>53</v>
+        <v>30.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>-6.59</v>
+        <v>15.91</v>
       </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
@@ -3327,10 +3163,10 @@
         <v>49.27</v>
       </c>
       <c r="P46" t="n">
-        <v>55</v>
+        <v>35.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>-9.84</v>
+        <v>9.66</v>
       </c>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -3386,16 +3222,12 @@
         <v>50.8</v>
       </c>
       <c r="P47" t="n">
-        <v>55</v>
+        <v>33.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>-10.21</v>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>11.59</v>
+      </c>
+      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3449,16 +3281,12 @@
         <v>47.54</v>
       </c>
       <c r="P48" t="n">
-        <v>85</v>
+        <v>61.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>-40.56</v>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>-16.76</v>
+      </c>
+      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -3512,10 +3340,10 @@
         <v>47.95</v>
       </c>
       <c r="P49" t="n">
-        <v>66</v>
+        <v>42.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>-22.43</v>
+        <v>0.77</v>
       </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
@@ -3571,10 +3399,10 @@
         <v>49.76</v>
       </c>
       <c r="P50" t="n">
-        <v>90</v>
+        <v>60.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>-47.68</v>
+        <v>-18.28</v>
       </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
@@ -3630,16 +3458,12 @@
         <v>47.08</v>
       </c>
       <c r="P51" t="n">
-        <v>54</v>
+        <v>36.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>-11.71</v>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>5.69</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -3693,10 +3517,10 @@
         <v>49.38</v>
       </c>
       <c r="P52" t="n">
-        <v>71</v>
+        <v>43.9</v>
       </c>
       <c r="Q52" t="n">
-        <v>-28.84</v>
+        <v>-1.74</v>
       </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
@@ -3752,16 +3576,12 @@
         <v>48.92</v>
       </c>
       <c r="P53" t="n">
-        <v>52</v>
+        <v>30.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>-10.09</v>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>11.71</v>
+      </c>
+      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -3815,16 +3635,12 @@
         <v>47.42</v>
       </c>
       <c r="P54" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="Q54" t="n">
-        <v>-8.18</v>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>6.82</v>
+      </c>
+      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -3878,16 +3694,12 @@
         <v>47.02</v>
       </c>
       <c r="P55" t="n">
-        <v>55</v>
+        <v>36.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>-14.72</v>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>3.48</v>
+      </c>
+      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -3941,16 +3753,12 @@
         <v>46.05</v>
       </c>
       <c r="P56" t="n">
-        <v>66</v>
+        <v>51.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>-26.97</v>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>-12.07</v>
+      </c>
+      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -4064,11 +3872,7 @@
       <c r="Q58" t="n">
         <v>13.75</v>
       </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -4122,10 +3926,10 @@
         <v>44.81</v>
       </c>
       <c r="P59" t="n">
-        <v>26</v>
+        <v>19.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>10.34</v>
+        <v>16.54</v>
       </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
@@ -4181,16 +3985,12 @@
         <v>41.35</v>
       </c>
       <c r="P60" t="n">
-        <v>53</v>
+        <v>30.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>-17.44</v>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>4.86</v>
+      </c>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -4299,16 +4099,12 @@
         <v>42.05</v>
       </c>
       <c r="P62" t="n">
-        <v>37</v>
+        <v>22.3</v>
       </c>
       <c r="Q62" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>12.68</v>
+      </c>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -4362,16 +4158,12 @@
         <v>42.95</v>
       </c>
       <c r="P63" t="n">
-        <v>28</v>
+        <v>17.3</v>
       </c>
       <c r="Q63" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>17.44</v>
+      </c>
+      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -4425,10 +4217,10 @@
         <v>39.72</v>
       </c>
       <c r="P64" t="n">
-        <v>32</v>
+        <v>20.3</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.93</v>
+        <v>12.63</v>
       </c>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
@@ -4484,16 +4276,12 @@
         <v>28.42</v>
       </c>
       <c r="P65" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="Q65" t="n">
-        <v>6</v>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>8.1</v>
+      </c>
+      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
     </row>
   </sheetData>
@@ -4658,16 +4446,12 @@
         <v>200</v>
       </c>
       <c r="P2" t="n">
-        <v>264</v>
+        <v>253.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>-16.69</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+        <v>-5.99</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -4721,16 +4505,12 @@
         <v>193.03</v>
       </c>
       <c r="P3" t="n">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -4784,16 +4564,12 @@
         <v>205.47</v>
       </c>
       <c r="P4" t="n">
-        <v>198</v>
+        <v>185.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>39.45</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>51.65</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -4847,16 +4623,12 @@
         <v>181.94</v>
       </c>
       <c r="P5" t="n">
-        <v>269</v>
+        <v>260.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>-49.14</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>-40.24</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -4910,16 +4682,12 @@
         <v>174.37</v>
       </c>
       <c r="P6" t="n">
-        <v>200</v>
+        <v>187.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+        <v>21.91</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -4973,16 +4741,12 @@
         <v>172.74</v>
       </c>
       <c r="P7" t="n">
-        <v>207</v>
+        <v>197.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>-12.52</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+        <v>-3.02</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -5036,16 +4800,12 @@
         <v>150.35</v>
       </c>
       <c r="P8" t="n">
-        <v>229</v>
+        <v>225.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>-34.6</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+        <v>-31</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -5099,16 +4859,12 @@
         <v>157.02</v>
       </c>
       <c r="P9" t="n">
-        <v>208</v>
+        <v>202.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>-16.98</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>-11.78</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -5162,16 +4918,12 @@
         <v>169.8</v>
       </c>
       <c r="P10" t="n">
-        <v>208</v>
+        <v>195.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>-23.63</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+        <v>-11.23</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -5225,16 +4977,12 @@
         <v>154.07</v>
       </c>
       <c r="P11" t="n">
-        <v>189</v>
+        <v>184.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.38</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+        <v>-1.98</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -5288,16 +5036,12 @@
         <v>154.61</v>
       </c>
       <c r="P12" t="n">
-        <v>172</v>
+        <v>163.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+        <v>9.48</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -5351,16 +5095,12 @@
         <v>144.88</v>
       </c>
       <c r="P13" t="n">
-        <v>166</v>
+        <v>160.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+        <v>9.73</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -5414,16 +5154,12 @@
         <v>143.56</v>
       </c>
       <c r="P14" t="n">
-        <v>156</v>
+        <v>151.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+        <v>16.95</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -5477,16 +5213,12 @@
         <v>148.43</v>
       </c>
       <c r="P15" t="n">
-        <v>160</v>
+        <v>146.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+        <v>17.26</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -5540,16 +5272,12 @@
         <v>134.78</v>
       </c>
       <c r="P16" t="n">
-        <v>146</v>
+        <v>132.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>21.39</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -5603,16 +5331,12 @@
         <v>138.43</v>
       </c>
       <c r="P17" t="n">
-        <v>167</v>
+        <v>160.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>-13.79</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>-7.59</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -5666,16 +5390,12 @@
         <v>134.07</v>
       </c>
       <c r="P18" t="n">
-        <v>175</v>
+        <v>160.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>-34.11</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+        <v>-20.01</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -5729,16 +5449,12 @@
         <v>123.48</v>
       </c>
       <c r="P19" t="n">
-        <v>153</v>
+        <v>147.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>-12.96</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+        <v>-7.76</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -5792,16 +5508,12 @@
         <v>121.53</v>
       </c>
       <c r="P20" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>37.99</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>66.59</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -5855,16 +5567,12 @@
         <v>120.23</v>
       </c>
       <c r="P21" t="n">
-        <v>154</v>
+        <v>140.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>-19.69</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+        <v>-5.89</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -5918,16 +5626,12 @@
         <v>125.37</v>
       </c>
       <c r="P22" t="n">
-        <v>170</v>
+        <v>163.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>-37.13</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>-30.33</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -5981,16 +5685,12 @@
         <v>123.27</v>
       </c>
       <c r="P23" t="n">
-        <v>144</v>
+        <v>125.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>-11.43</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>7.27</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -6044,16 +5744,12 @@
         <v>122.86</v>
       </c>
       <c r="P24" t="n">
-        <v>139</v>
+        <v>123.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>-7.03</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>8.17</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -6107,16 +5803,12 @@
         <v>122.16</v>
       </c>
       <c r="P25" t="n">
-        <v>125</v>
+        <v>106.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>25.43</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -6170,16 +5862,12 @@
         <v>120.61</v>
       </c>
       <c r="P26" t="n">
-        <v>128</v>
+        <v>110.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+        <v>20.34</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -6233,16 +5921,12 @@
         <v>119.75</v>
       </c>
       <c r="P27" t="n">
-        <v>131</v>
+        <v>115.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+        <v>14.49</v>
+      </c>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -6296,16 +5980,12 @@
         <v>113.22</v>
       </c>
       <c r="P28" t="n">
-        <v>168</v>
+        <v>157.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>-38.57</v>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>-27.87</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -6359,16 +6039,12 @@
         <v>107.89</v>
       </c>
       <c r="P29" t="n">
-        <v>171</v>
+        <v>166.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>-47.25</v>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+        <v>-42.85</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -6422,16 +6098,12 @@
         <v>114.2</v>
       </c>
       <c r="P30" t="n">
-        <v>124</v>
+        <v>108.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>-5.43</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>9.67</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -6485,16 +6157,12 @@
         <v>98.48</v>
       </c>
       <c r="P31" t="n">
-        <v>133</v>
+        <v>121.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>-29.37</v>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+        <v>-17.97</v>
+      </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -6548,16 +6216,12 @@
         <v>95.15000000000001</v>
       </c>
       <c r="P32" t="n">
-        <v>64</v>
+        <v>38.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>27.95</v>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>53.65</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -6611,10 +6275,10 @@
         <v>78.91</v>
       </c>
       <c r="P33" t="n">
-        <v>127</v>
+        <v>107.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>-58.06</v>
+        <v>-38.66</v>
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -6781,16 +6445,12 @@
         <v>77.84</v>
       </c>
       <c r="P2" t="n">
-        <v>155</v>
+        <v>140.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>-66.5</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>-51.8</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -6844,16 +6504,12 @@
         <v>81.37</v>
       </c>
       <c r="P3" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+        <v>26.56</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -6907,16 +6563,12 @@
         <v>80.20999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>112</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-31.94</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>-4.84</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -6970,16 +6622,12 @@
         <v>70.40000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="n">
-        <v>-44.39</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+        <v>-23.39</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -7033,16 +6681,12 @@
         <v>66.64</v>
       </c>
       <c r="P6" t="n">
-        <v>116</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-41.57</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+        <v>-20.47</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -7096,16 +6740,12 @@
         <v>69.34999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>80</v>
+        <v>56.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>-7.78</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>15.82</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -7159,16 +6799,12 @@
         <v>69.39</v>
       </c>
       <c r="P8" t="n">
-        <v>90</v>
+        <v>69.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>-19.11</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+        <v>1.19</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -7222,16 +6858,12 @@
         <v>56.23</v>
       </c>
       <c r="P9" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="Q9" t="n">
-        <v>-33.53</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+        <v>-10.53</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -7285,16 +6917,12 @@
         <v>53.25</v>
       </c>
       <c r="P10" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="Q10" t="n">
-        <v>-24.98</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -7348,10 +6976,10 @@
         <v>50.69</v>
       </c>
       <c r="P11" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="Q11" t="n">
-        <v>-17.34</v>
+        <v>5.66</v>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -7407,16 +7035,12 @@
         <v>49.73</v>
       </c>
       <c r="P12" t="n">
-        <v>84</v>
+        <v>63.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>-37.42</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+        <v>-17.22</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -7470,10 +7094,10 @@
         <v>53.12</v>
       </c>
       <c r="P13" t="n">
-        <v>53</v>
+        <v>30.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.59</v>
+        <v>15.91</v>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -7529,10 +7153,10 @@
         <v>49.27</v>
       </c>
       <c r="P14" t="n">
-        <v>55</v>
+        <v>35.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.84</v>
+        <v>9.66</v>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -7588,16 +7212,12 @@
         <v>50.8</v>
       </c>
       <c r="P15" t="n">
-        <v>55</v>
+        <v>33.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>-10.21</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>11.59</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -7651,16 +7271,12 @@
         <v>47.54</v>
       </c>
       <c r="P16" t="n">
-        <v>85</v>
+        <v>61.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>-40.56</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>-16.76</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -7714,10 +7330,10 @@
         <v>47.95</v>
       </c>
       <c r="P17" t="n">
-        <v>66</v>
+        <v>42.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>-22.43</v>
+        <v>0.77</v>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
@@ -7773,10 +7389,10 @@
         <v>49.76</v>
       </c>
       <c r="P18" t="n">
-        <v>90</v>
+        <v>60.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>-47.68</v>
+        <v>-18.28</v>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -7832,16 +7448,12 @@
         <v>47.08</v>
       </c>
       <c r="P19" t="n">
-        <v>54</v>
+        <v>36.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>-11.71</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>5.69</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -7895,10 +7507,10 @@
         <v>49.38</v>
       </c>
       <c r="P20" t="n">
-        <v>71</v>
+        <v>43.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>-28.84</v>
+        <v>-1.74</v>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -7954,16 +7566,12 @@
         <v>48.92</v>
       </c>
       <c r="P21" t="n">
-        <v>52</v>
+        <v>30.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>-10.09</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>11.71</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -8017,16 +7625,12 @@
         <v>47.42</v>
       </c>
       <c r="P22" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="Q22" t="n">
-        <v>-8.18</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>6.82</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -8080,16 +7684,12 @@
         <v>47.02</v>
       </c>
       <c r="P23" t="n">
-        <v>55</v>
+        <v>36.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>-14.72</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>3.48</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -8143,16 +7743,12 @@
         <v>46.05</v>
       </c>
       <c r="P24" t="n">
-        <v>66</v>
+        <v>51.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>-26.97</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>-12.07</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -8266,11 +7862,7 @@
       <c r="Q26" t="n">
         <v>13.75</v>
       </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -8324,10 +7916,10 @@
         <v>44.81</v>
       </c>
       <c r="P27" t="n">
-        <v>26</v>
+        <v>19.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>10.34</v>
+        <v>16.54</v>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
@@ -8383,16 +7975,12 @@
         <v>41.35</v>
       </c>
       <c r="P28" t="n">
-        <v>53</v>
+        <v>30.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>-17.44</v>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>4.86</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -8501,16 +8089,12 @@
         <v>42.05</v>
       </c>
       <c r="P30" t="n">
-        <v>37</v>
+        <v>22.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>12.68</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -8564,16 +8148,12 @@
         <v>42.95</v>
       </c>
       <c r="P31" t="n">
-        <v>28</v>
+        <v>17.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>17.44</v>
+      </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -8627,10 +8207,10 @@
         <v>39.72</v>
       </c>
       <c r="P32" t="n">
-        <v>32</v>
+        <v>20.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.93</v>
+        <v>12.63</v>
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -8686,16 +8266,12 @@
         <v>28.42</v>
       </c>
       <c r="P33" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+        <v>8.1</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
     </row>
   </sheetData>
